--- a/workspaces/btc_daily_14days/volume/volume_ratio_14.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_14.xlsx
@@ -575,46 +575,46 @@
         <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-9.810511490941131</v>
+        <v>-9.781246990187981</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.886258617209393</v>
+        <v>-2.877152067317994</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.50213551090161</v>
+        <v>-4.488606284115214</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-12.91588431150953</v>
+        <v>-12.87719855753711</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.79596803537747</v>
+        <v>-9.766356437414395</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.500555851472576</v>
+        <v>-9.471995163957487</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.366574319768382</v>
+        <v>-8.341179854547548</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.393469016704735</v>
+        <v>-6.373869723546392</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8.899932260628781</v>
+        <v>-8.873124427868532</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.19847493466272</v>
+        <v>-1.194641943507321</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.263368749707325</v>
+        <v>2.256454509767586</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.743475217551193</v>
+        <v>4.729213697299649</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.768757797254374</v>
+        <v>6.748687905675531</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.318027519299882</v>
+        <v>-0.3169914418148423</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.988387815159932</v>
+        <v>-2.004308953380878</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.471576458786359</v>
+        <v>3.495517529795954</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.098626894445751</v>
+        <v>5.135338004844243</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1757452645973387</v>
+        <v>0.1749597921134693</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.670125007748702</v>
+        <v>2.687531180029765</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.99141979468645</v>
+        <v>5.026385428744973</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.907688633501266</v>
+        <v>4.941641659144693</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.464678004506965</v>
+        <v>6.510126657431705</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.417400518701214</v>
+        <v>7.47021248559512</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.158820964360359</v>
+        <v>9.225464570975419</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>10.97840835836642</v>
+        <v>11.05995972453877</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.96543322232953</v>
+        <v>7.01762747186288</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.537814904940966</v>
+        <v>5.579174287775956</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.775033860527046</v>
+        <v>4.809937378493764</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.740191566963226</v>
+        <v>-5.804245795319268</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.157570762619699</v>
+        <v>-2.182210812711638</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.497643208762163</v>
+        <v>-3.535045845492597</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.609445864442065</v>
+        <v>-5.672706984186533</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.245026797435578</v>
+        <v>-2.271768591833357</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.953382582565887</v>
+        <v>-1.975669530003394</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.036974665447076</v>
+        <v>-2.060773159101693</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.499803459827184</v>
+        <v>-2.528102161278611</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.991084924366206</v>
+        <v>2.011760564777433</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1522215228919279</v>
+        <v>-0.1525700791188953</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3575591777898239</v>
+        <v>-0.3573643437959788</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.924974591426654</v>
+        <v>-2.953131195874306</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.641946399830765</v>
+        <v>-4.689397836428654</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.092792946756752</v>
+        <v>-3.125078733214067</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.383104889666711</v>
+        <v>7.410561632515623</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.538160417122526</v>
+        <v>4.555268447232962</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.525754702945655</v>
+        <v>3.539246061805201</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.04879981773125053</v>
+        <v>-0.05108602399855755</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.440463806036334</v>
+        <v>-2.451546381524963</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.761231647596553</v>
+        <v>-2.773030655984272</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3750717157124015</v>
+        <v>-0.3776402185428296</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.079335140681223</v>
+        <v>-2.0885705634633</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.758966146689531</v>
+        <v>-2.769871272661497</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.518761219495957</v>
+        <v>-0.5203519185844243</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.433317517363562</v>
+        <v>-4.449436601458174</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.163378162270163</v>
+        <v>-3.175176711479381</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.492441901417294</v>
+        <v>-0.4942420728480386</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.749063698465257</v>
+        <v>-1.7561673242569</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.237028063799833</v>
+        <v>-2.257609678081486</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.279968380172534</v>
+        <v>1.290621273808163</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.423915448268744</v>
+        <v>2.444909103186014</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.579980351064449</v>
+        <v>3.605958331258329</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.581545296606649</v>
+        <v>4.616787450460357</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.907121161284117</v>
+        <v>5.954873281194764</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.770277669276446</v>
+        <v>3.800051093489891</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.074075483740167</v>
+        <v>3.097452448171502</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.98606936600688</v>
+        <v>2.00217386057021</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.65186617777421</v>
+        <v>1.666901784524825</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.961096296650055</v>
+        <v>1.97958646045295</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.797964552345398</v>
+        <v>2.822489533013503</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.8412978865034759</v>
+        <v>0.8486796181747636</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.117524128567617</v>
+        <v>2.134670380502854</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.333774454663761</v>
+        <v>-3.359929387191073</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.425095800655576</v>
+        <v>-2.44232033127853</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5423590746627696</v>
+        <v>0.5474368367508617</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.93338478092906</v>
+        <v>1.944575965710079</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.7860193682615559</v>
+        <v>0.7899576380702626</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1795007564408166</v>
+        <v>-0.1809594738539317</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2637670162825643</v>
+        <v>-0.2663975191698356</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.476538869366529</v>
+        <v>3.500175078405015</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.574793067215488</v>
+        <v>2.593318591613745</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.988672453695386</v>
+        <v>3.011635651238436</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.522079097515793</v>
+        <v>1.535321677693872</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1261642841265456</v>
+        <v>-0.1254598915639207</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1140743923469856</v>
+        <v>0.1153872672482663</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.624632572669292</v>
+        <v>1.636295040202519</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>260</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>2.503897409225537</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.434237124891425</v>
+        <v>2.431087046474964</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.424105401198013</v>
+        <v>2.420468929629941</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.44748361951973</v>
+        <v>-2.44375147778657</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.986068194331125</v>
+        <v>-2.981682613641247</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.159396055291474</v>
+        <v>1.157851914130397</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.08017205810928374</v>
+        <v>-0.07988382917351089</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1626367678707226</v>
+        <v>-0.162486278141273</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5467243413708545</v>
+        <v>0.5457069824748615</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.615105507391313</v>
+        <v>-2.61211051024538</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.205266614672411</v>
+        <v>-3.201479219178253</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.171145351696303</v>
+        <v>-3.167096061833</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.666456202778022</v>
+        <v>-1.664273749700804</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.571779694730417</v>
+        <v>-2.568398571270755</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.585111528732547</v>
+        <v>1.591393705686833</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.444308159273106</v>
+        <v>-2.45695121348605</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.16373179861035</v>
+        <v>-6.193985018146002</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.731567834447524</v>
+        <v>-5.764601025905321</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.363493146592276</v>
+        <v>-5.394461625716026</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-6.579419000620568</v>
+        <v>-6.613941661001661</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.684464751888946</v>
+        <v>-4.710061345354113</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.360428174791473</v>
+        <v>-6.393888412758393</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7.464983691843678</v>
+        <v>-7.503159045114508</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-10.72936512658077</v>
+        <v>-10.78489517239174</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-8.816397855002911</v>
+        <v>-8.861988922241309</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.571525257412382</v>
+        <v>-7.611800293771118</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.175318937094723</v>
+        <v>-6.208346698029303</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.833737224087798</v>
+        <v>-6.870479469096338</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5703613971329844</v>
+        <v>-0.5726256656072124</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.023535503552552</v>
+        <v>1.025680710332594</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9747956449178119</v>
+        <v>-0.9782802237147195</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.682262847535299</v>
+        <v>2.686075012676703</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.708872311423328</v>
+        <v>4.718500861958432</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.977703404434664</v>
+        <v>1.981033086862809</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.099731109555741</v>
+        <v>5.111733453191817</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.709909982369673</v>
+        <v>2.715289604249541</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.328147946370464</v>
+        <v>2.332746309707112</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.802225214266308</v>
+        <v>1.804164533039312</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.276817249603845</v>
+        <v>1.277867800361605</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.95272470658324</v>
+        <v>1.955337774427285</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.174531942632775</v>
+        <v>2.178169980202647</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.744585386837741</v>
+        <v>2.74943472083914</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>366</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.493438320210011</v>
+        <v>-2.491932927051479</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2800984737387253</v>
+        <v>-0.2798753211523177</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.78497373886848</v>
+        <v>1.784272365693788</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.188314827859372</v>
+        <v>2.187749542017066</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.376431863055437</v>
+        <v>1.376104283228983</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8540025174298123</v>
+        <v>0.8538740897971024</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.8707541115364421</v>
+        <v>-0.8702038897701954</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.791621425045463</v>
+        <v>-0.7909392011199969</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.03251640704375092</v>
+        <v>-0.03226695615487785</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3366525759789099</v>
+        <v>-0.3359440537510565</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.268060960986098</v>
+        <v>-0.2674733343527862</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.42062421479821</v>
+        <v>-2.418882526734123</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.747522430585633</v>
+        <v>-1.746240962815513</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4042344443936372</v>
+        <v>-0.4036234556760974</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6315616797900603</v>
+        <v>0.6306880311022525</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.62273236612041</v>
+        <v>-3.634792497437623</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.641446109675776</v>
+        <v>-4.656620451683082</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.259378035146398</v>
+        <v>-3.272448823777744</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.546974276617739</v>
+        <v>-2.55695154355211</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.06318730194323052</v>
+        <v>-0.0651522390652417</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.273251008655905</v>
+        <v>-3.284682194582153</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.48779449191467</v>
+        <v>-2.497947098065843</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.61178936225744</v>
+        <v>-1.618508112774656</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.019464705680441</v>
+        <v>-4.036031416924942</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.911718029997985</v>
+        <v>-3.927305117418037</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.626014914891122</v>
+        <v>-2.639003464774795</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.421104531115901</v>
+        <v>-2.43229882807087</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.110203156600925</v>
+        <v>-3.123016367267795</v>
       </c>
     </row>
     <row r="17">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.4848</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4082~4094</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4082</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.02641340570093575</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.5366</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4000~4012</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4000</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.1735606827810443</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.5884</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3902~3913</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3902</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.2282585875334462</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.6402</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3750~3759</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3750</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.4727760985184091</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.692</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3589~3597</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3589</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.1615519494591879</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.7438</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3396~3402</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3396</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.2990366944872633</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.7956</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3160~3164</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3160</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.5723012499543714</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.8474</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2900~2904</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2900</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.3991236632611006</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.8992</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2571~2573</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2571</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.2465539067624363</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.951</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2260~2261</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2260</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.3592817151725995</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 1.003</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1894~1895</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1894</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.9102556111884468</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 1.055</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1575~1575</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1575</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.966879140107487</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 1.106</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1292~1292</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1292</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.8347350544030334</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 1.158</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1078~1078</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1078</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.959251846765909</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 1.21</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>881~881</t>
-        </is>
+      <c r="B20" t="n">
+        <v>881</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.309058842105578</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 1.262</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>711~711</t>
-        </is>
+      <c r="B21" t="n">
+        <v>711</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.640176307075535</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 1.314</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>601~601</t>
-        </is>
+      <c r="B22" t="n">
+        <v>601</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>3.746162345347422</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 1.365</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>500~500</t>
-        </is>
+      <c r="B23" t="n">
+        <v>500</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.90656167979003</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 1.417</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>428~428</t>
-        </is>
+      <c r="B24" t="n">
+        <v>428</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.179458876051704</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 1.469</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>362~362</t>
-        </is>
+      <c r="B25" t="n">
+        <v>362</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.926451182552455</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 1.521</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>305~305</t>
-        </is>
+      <c r="B26" t="n">
+        <v>305</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.277053483068713</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 1.573</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>262~262</t>
-        </is>
+      <c r="B27" t="n">
+        <v>262</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.9416761836068162</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 1.624</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>221~221</t>
-        </is>
+      <c r="B28" t="n">
+        <v>221</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.9002268381610676</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 1.676</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>194~194</t>
-        </is>
+      <c r="B29" t="n">
+        <v>194</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.4315826501068756</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 1.728</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>163~163</t>
-        </is>
+      <c r="B30" t="n">
+        <v>163</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.2672978761090405</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 1.78</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>148~148</t>
-        </is>
+      <c r="B31" t="n">
+        <v>148</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.560615733844081</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 1.832</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>121~121</t>
-        </is>
+      <c r="B32" t="n">
+        <v>121</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.878462506236311</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1.883</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>112~112</t>
-        </is>
+      <c r="B33" t="n">
+        <v>112</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>2.863704536932886</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1.935</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>97~97</t>
-        </is>
+      <c r="B34" t="n">
+        <v>97</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.145736937521981</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1.987</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.4848</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2.268466441694791</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.5366</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>165~166</t>
-        </is>
+      <c r="B7" t="n">
+        <v>165</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-3.69825759731841</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.5884</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>263~265</t>
-        </is>
+      <c r="B8" t="n">
+        <v>263</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-3.059476056059033</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.6402</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>415~419</t>
-        </is>
+      <c r="B9" t="n">
+        <v>415</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-4.044750969374654</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.692</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>576~581</t>
-        </is>
+      <c r="B10" t="n">
+        <v>576</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.8583264441342422</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.7438</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>769~776</t>
-        </is>
+      <c r="B11" t="n">
+        <v>769</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.204778526395543</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.7956</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1005~1014</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1005</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.704483685101494</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.8474</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1265~1274</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1265</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.8450866718583185</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.8992</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1594~1605</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1594</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.3439056099295996</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.951</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1905~1917</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1905</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.3807622638719508</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 1.003</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2271~2283</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2271</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.7194567170562323</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 1.055</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2590~2603</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2590</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.5533691692303364</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 1.106</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2873~2886</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2873</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.345136171907825</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 1.158</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3087~3100</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3087</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.6547286427906158</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 1.21</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3284~3297</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3284</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.3248001643106733</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 1.262</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3454~3467</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3454</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.51766675978309</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 1.314</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3564~3577</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3564</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.6063821278700203</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 1.365</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3665~3678</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3665</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.3727205388070374</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 1.417</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3737~3750</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3737</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.2267716535433166</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 1.469</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3803~3816</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3803</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1611532049060003</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 1.521</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3860~3873</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3860</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.0792890818934211</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 1.573</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3903~3916</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3903</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.04195721704347477</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 1.624</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3944~3957</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3944</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.0294504506117903</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 1.676</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3971~3984</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3971</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.04170224203902251</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 1.728</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>4002~4015</t>
-        </is>
+      <c r="B30" t="n">
+        <v>4002</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.009675004821161792</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 1.78</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4017~4030</t>
-        </is>
+      <c r="B31" t="n">
+        <v>4017</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.03686263782783783</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 1.832</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4044~4057</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4044</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.06553592928071339</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1.883</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4053~4066</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4053</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.05861293899993569</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1.935</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4068~4081</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4068</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.03080661229524395</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1.987</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.001987416448372414</v>

--- a/workspaces/btc_daily_14days/volume/volume_ratio_14.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-9.781246990187981</v>
+        <v>-9.76877030580097</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.877152067317994</v>
+        <v>-2.86428067890418</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.488606284115214</v>
+        <v>-4.475635173607387</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-12.87719855753711</v>
+        <v>-12.86425648130241</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.766356437414395</v>
+        <v>-9.753277391118722</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.471995163957487</v>
+        <v>-9.458979764802976</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.341179854547548</v>
+        <v>-8.328136843557644</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.373869723546392</v>
+        <v>-6.3607076433481</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8.873124427868532</v>
+        <v>-8.859941430588378</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.194641943507321</v>
+        <v>-1.181247352638991</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.256454509767586</v>
+        <v>2.270487990138797</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.729213697299649</v>
+        <v>4.742659703763302</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.748687905675531</v>
+        <v>6.762240899406322</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3169914418148423</v>
+        <v>-0.3274210775124473</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>98</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.004308953380878</v>
+        <v>-1.991691573616137</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.495517529795954</v>
+        <v>3.508532697764892</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.135338004844243</v>
+        <v>5.148455390449392</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1749597921134693</v>
+        <v>0.1880497863289179</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.687531180029765</v>
+        <v>2.700758705600272</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.026385428744973</v>
+        <v>5.039548639424815</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.941641659144693</v>
+        <v>4.954831740097319</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.510126657431705</v>
+        <v>6.523436237328987</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.47021248559512</v>
+        <v>7.483543227688877</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.225464570975419</v>
+        <v>8.668341023143157</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.05995972453877</v>
+        <v>11.0762759365393</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.01762747186288</v>
+        <v>7.031073517195601</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.579174287775956</v>
+        <v>5.592727083750333</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.809937378493764</v>
+        <v>4.79950774279515</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>152</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.804245795319268</v>
+        <v>-5.791582785274258</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.182210812711638</v>
+        <v>-2.169149811225509</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.535045845492597</v>
+        <v>-3.880622714653391</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.672706984186533</v>
+        <v>-6.020151686850021</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.271768591833357</v>
+        <v>-2.258685313733224</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.975669530003394</v>
+        <v>-1.962649889072402</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.060773159101693</v>
+        <v>-2.047726393099154</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.528102161278611</v>
+        <v>-2.51493698651052</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.011760564777433</v>
+        <v>2.024948407030699</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1525700791188953</v>
+        <v>-0.1391737051617028</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3573643437959788</v>
+        <v>-0.3439021569946945</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.953131195874306</v>
+        <v>-2.939686918358696</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.689397836428654</v>
+        <v>-4.675845961088569</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.125078733214067</v>
+        <v>-3.135508368911921</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.410561632515623</v>
+        <v>7.378306517876545</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.555268447232962</v>
+        <v>4.540267364471212</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.539246061805201</v>
+        <v>3.531209956827425</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.05108602399855755</v>
+        <v>-0.03454095622215192</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.451546381524963</v>
+        <v>-2.420404145441303</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.773030655984272</v>
+        <v>-2.740784336791201</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3776402185428296</v>
+        <v>-0.3604086173457404</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.0885705634633</v>
+        <v>-2.060355490171972</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.769871272661497</v>
+        <v>-2.738913084329276</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5203519185844243</v>
+        <v>-0.5044656874860891</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.449436601458174</v>
+        <v>-4.410837459501309</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.175176711479381</v>
+        <v>-3.142504795579882</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4942420728480386</v>
+        <v>-0.4777564789044249</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.7561673242569</v>
+        <v>-1.486710448184482</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>193</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.257609678081486</v>
+        <v>-2.24425525979278</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.290621273808163</v>
+        <v>1.303292184188415</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.444909103186014</v>
+        <v>2.457916234603616</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.605958331258329</v>
+        <v>3.618937473656793</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.616787450460357</v>
+        <v>4.628816992276839</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.954873281194764</v>
+        <v>5.966405592567433</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.800051093489891</v>
+        <v>3.812232686148811</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.097452448171502</v>
+        <v>2.82332543156766</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.00217386057021</v>
+        <v>2.014886232329857</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.666901784524825</v>
+        <v>1.680306912177656</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.97958646045295</v>
+        <v>1.993043754163168</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.822489533013503</v>
+        <v>2.544995953672661</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.8486796181747636</v>
+        <v>0.8619756036179353</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.134670380502854</v>
+        <v>2.124240744804702</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>236</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.359929387191073</v>
+        <v>-3.34614427126764</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.44232033127853</v>
+        <v>-2.428534508328205</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5474368367508617</v>
+        <v>0.5604439681684639</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.944575965710079</v>
+        <v>1.957555108108544</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.7899576380702626</v>
+        <v>0.5697380015420777</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1809594738539317</v>
+        <v>-0.1677992775365098</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2663975191698356</v>
+        <v>-0.2531568128090029</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.500175078405015</v>
+        <v>3.513356087700252</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.593318591613745</v>
+        <v>2.605761151872962</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.011635651238436</v>
+        <v>3.025040778891267</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.535321677693872</v>
+        <v>1.54877897140409</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1254598915639207</v>
+        <v>-0.1120076028438106</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1153872672482663</v>
+        <v>-0.1107996300742471</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.636295040202519</v>
+        <v>1.625865404504367</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>260</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.503897409225537</v>
+        <v>2.515725919799117</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.431087046474964</v>
+        <v>2.443186803082682</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.420468929629941</v>
+        <v>2.433476061047543</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.44375147778657</v>
+        <v>-2.430772335388106</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.981682613641247</v>
+        <v>-2.968571809266308</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.157851914130397</v>
+        <v>1.170491319189999</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.07988382917351089</v>
+        <v>-0.06675751666342933</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.162486278141273</v>
+        <v>-0.1493052688460352</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5457069824748615</v>
+        <v>0.5586454681486828</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.61211051024538</v>
+        <v>-2.598705382592549</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.201479219178253</v>
+        <v>-3.188021925468036</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.167096061833</v>
+        <v>-3.15364377311289</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.664273749700804</v>
+        <v>-1.650717703349201</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.568398571270755</v>
+        <v>-2.578828206968907</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>329</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.591393705686833</v>
+        <v>1.60354213163275</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.45695121348605</v>
+        <v>-2.44301025950022</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.193985018146002</v>
+        <v>-6.1809778867284</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.764601025905321</v>
+        <v>-5.751621883506857</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.394461625716026</v>
+        <v>-5.381350821341087</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-6.613941661001661</v>
+        <v>-6.598244483808699</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.710061345354113</v>
+        <v>-4.863576734614036</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.393888412758393</v>
+        <v>-6.380707403463155</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7.503159045114508</v>
+        <v>-7.65697115767415</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-10.78489517239174</v>
+        <v>-10.77149004473891</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-8.861988922241309</v>
+        <v>-8.848531628531092</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.611800293771118</v>
+        <v>-7.598348005051008</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.208346698029303</v>
+        <v>-6.1947906516777</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.870479469096338</v>
+        <v>-6.88090910479449</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>311</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5726256656072124</v>
+        <v>-0.559693519445922</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.025680710332594</v>
+        <v>1.038305815351954</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9782802237147195</v>
+        <v>-0.9652730922971173</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.686075012676703</v>
+        <v>2.699054155075167</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.718500861958432</v>
+        <v>4.731611666333372</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.981033086862809</v>
+        <v>1.816051949912691</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.111733453191817</v>
+        <v>5.124799707492294</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.715289604249541</v>
+        <v>2.728470613544779</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.332746309707112</v>
+        <v>2.345945048661875</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.804164533039312</v>
+        <v>1.817569660692143</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.277867800361605</v>
+        <v>1.291325094071823</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.955337774427285</v>
+        <v>1.968790063147395</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.178169980202647</v>
+        <v>2.19172602655425</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.74943472083914</v>
+        <v>2.739005085140988</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>366</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.491932927051479</v>
+        <v>-2.47793147931764</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2798753211523177</v>
+        <v>-0.266755137872309</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.784272365693788</v>
+        <v>1.79727949711139</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.187749542017066</v>
+        <v>2.20072868441553</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.376104283228983</v>
+        <v>1.389215087603922</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8538740897971024</v>
+        <v>0.8669169860914678</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.8702038897701954</v>
+        <v>-0.8571376354697193</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7909392011199969</v>
+        <v>-0.7777581918247591</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.03226695615487785</v>
+        <v>-0.01906821720011465</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3359440537510565</v>
+        <v>-0.3225389260982254</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.2674733343527862</v>
+        <v>-0.2540160406425684</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.418882526734123</v>
+        <v>-2.405430238014013</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.746240962815513</v>
+        <v>-1.73268491646391</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4036234556760974</v>
+        <v>-0.4140530913742495</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>319</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6306880311022525</v>
+        <v>0.6434580794555487</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.634792497437623</v>
+        <v>-3.792104604967271</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.656620451683082</v>
+        <v>-4.64361332026548</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.272448823777744</v>
+        <v>-3.259469681379279</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.55695154355211</v>
+        <v>-2.54384073917717</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.0651522390652417</v>
+        <v>-0.05210934277087631</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.284682194582153</v>
+        <v>-3.271615940281677</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.497947098065843</v>
+        <v>-2.484766088770606</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.618508112774656</v>
+        <v>-1.605309373819892</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.036031416924942</v>
+        <v>-4.022626289272111</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.927305117418037</v>
+        <v>-3.913847823707819</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.639003464774795</v>
+        <v>-2.625551176054685</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.43229882807087</v>
+        <v>-2.418742781719267</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.123016367267795</v>
+        <v>-3.133446002965947</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>283</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.570165920072704</v>
+        <v>1.582195395903604</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.574976597485225</v>
+        <v>-3.562066787909174</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4362763994881718</v>
+        <v>-0.4232692680705696</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.460761185416146</v>
+        <v>1.47374032781461</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.197801372412165</v>
+        <v>-1.184690568037226</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1597112366815381</v>
+        <v>0.1727541329759035</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7816913003280277</v>
+        <v>0.7947575546285037</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.727935463383993</v>
+        <v>1.741116472679231</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.140433810417235</v>
+        <v>4.153632549371999</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>7.177234420442346</v>
+        <v>7.190639548095177</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.792269081990412</v>
+        <v>3.80572637570063</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.533366020254611</v>
+        <v>4.546818308974721</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.699683847472301</v>
+        <v>2.713239893823904</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.242691398829812</v>
+        <v>2.23226176313166</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>214</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.829886918340819</v>
+        <v>-4.8121529713722</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.637722213548017</v>
+        <v>-3.624812403971966</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.967170359396988</v>
+        <v>-4.954163227979386</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.369627507163266</v>
+        <v>-4.356648364764801</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7024412455999851</v>
+        <v>-0.6893304412250458</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.54518622377222</v>
+        <v>-5.532143327477854</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.162630221418226</v>
+        <v>-5.14956396711775</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.695234180947395</v>
+        <v>-4.682053171652157</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-8.96184154376526</v>
+        <v>-8.948642804810497</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.008228411036178</v>
+        <v>-6.994823283383347</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.745692015727535</v>
+        <v>-6.732234722017317</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.842149979877433</v>
+        <v>-4.828697691157323</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.86053543194388</v>
+        <v>-3.846979385592277</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.610814099667593</v>
+        <v>-3.621243735365745</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.866967771160589</v>
+        <v>4.603336638086262</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.255394158196331</v>
+        <v>3.268303967772383</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.845297025203799</v>
+        <v>1.858304156621401</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8.574534929384932</v>
+        <v>8.587514071783396</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.482814221926944</v>
+        <v>4.495925026301883</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.287870372840601</v>
+        <v>5.300913269134966</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.634608736786511</v>
+        <v>0.647674991086987</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.182653764400975</v>
+        <v>1.195834773696212</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1064254518227656</v>
+        <v>0.1196241907775288</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.824828185576514</v>
+        <v>3.838233313229345</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.620074861258992</v>
+        <v>3.63353215496921</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.162072231802327</v>
+        <v>4.175524520522437</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.249431834055393</v>
+        <v>4.262987880406996</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.468696313539866</v>
+        <v>2.458266677841713</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>170</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.258144202562917</v>
+        <v>-4.245621912887295</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.953811596237493</v>
+        <v>2.966721405813544</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.970707595523258</v>
+        <v>1.98371472694086</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.100960728130758</v>
+        <v>2.113939870529222</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.150774807176269</v>
+        <v>2.163885611551208</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.09527556842138551</v>
+        <v>0.1083184647157509</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.128188909972565</v>
+        <v>4.141255164273041</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.837476099426318</v>
+        <v>4.850657108721556</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.011770330891153</v>
+        <v>3.024969069845916</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.514586322333834</v>
+        <v>4.527991449986665</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.898068292133878</v>
+        <v>4.911525585844096</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7.285392625949889</v>
+        <v>7.298844914669999</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6.865138015004959</v>
+        <v>6.878694061356562</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6.526624053163602</v>
+        <v>6.516194417465449</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>110</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.402529229300832</v>
+        <v>-3.390006939625209</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.377739205901456</v>
+        <v>-1.364829396325405</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.04557390568377429</v>
+        <v>0.05858103710137641</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.642354779890603</v>
+        <v>-1.629375637492139</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.273769459582688</v>
+        <v>3.286880263957627</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.571211397298406</v>
+        <v>3.584254293592771</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.668295861844307</v>
+        <v>1.681362116144783</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2920215539718924</v>
+        <v>0.3052025632671302</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.049203485971361</v>
+        <v>2.062402224926124</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6191035172383366</v>
+        <v>-0.6056983895855055</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.846889952153106</v>
+        <v>2.860342240873216</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3006373860644729</v>
+        <v>-0.28708133971287</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8581748553027211</v>
+        <v>0.8477452196045689</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>101</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>7.902601283750307</v>
+        <v>7.91512357342593</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.30092866088517</v>
+        <v>5.313838470461221</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.896158964189624</v>
+        <v>5.909166095607226</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.046214076995149</v>
+        <v>4.059193219393613</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.442702187581965</v>
+        <v>-1.429591383207026</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8349377699355003</v>
+        <v>0.8479806662298657</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.229993967138583</v>
+        <v>-1.216927712838107</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.263218673683866</v>
+        <v>2.276399682979104</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.212119777600584</v>
+        <v>1.225318516555348</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3619945925725929</v>
+        <v>0.375399720225424</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8328577416459666</v>
+        <v>-0.8194004479357488</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.778672604102518</v>
+        <v>-2.765220315382408</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.198927215047419</v>
+        <v>-3.185371168695816</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.959106872870144</v>
+        <v>-1.969536508568297</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>72</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7.228783902012324</v>
+        <v>7.241306191687947</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.061654733492432</v>
+        <v>0.07456454306848315</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-8.666547306437572</v>
+        <v>-8.65354017501997</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-8.536294173830072</v>
+        <v>-8.523315031431608</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-9.074715388902241</v>
+        <v>-9.061604584527302</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.999495673408646</v>
+        <v>-5.98645277711428</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.306451612903302</v>
+        <v>-3.293385358602826</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9958572339070599</v>
+        <v>-0.9826762246118221</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.22352378675599</v>
+        <v>-5.210325047801227</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.462537860672732</v>
+        <v>-7.449132733019901</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.025663528535631</v>
+        <v>-5.036093164233783</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>66</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.56716774039608</v>
+        <v>3.579690030071703</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.04557390568367481</v>
+        <v>0.05858103710127693</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.339324476860341</v>
+        <v>-1.326345334461877</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3625941767809948</v>
+        <v>-0.3494833724060555</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.640909814822905</v>
+        <v>-7.627866918528539</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-4.695340501792153</v>
+        <v>-4.682274247491677</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-9.707978446028157</v>
+        <v>-9.694797436732919</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-6.738675301907428</v>
+        <v>-6.725476562952664</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-7.588800486935398</v>
+        <v>-7.575395359282567</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.248099265798388</v>
+        <v>-3.23464197208817</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.213716108452957</v>
+        <v>-3.200263819732847</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.149122234549374</v>
+        <v>-5.135566188197771</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3539463568186676</v>
+        <v>-0.3643759925168197</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>57</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.401298521895292</v>
+        <v>5.413820811570915</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>9.052882803667927</v>
+        <v>9.065792613243978</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.903628132159049</v>
+        <v>6.916635263576651</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.246820489619417</v>
+        <v>-5.233841347220952</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.539627669603867</v>
+        <v>-7.526516865228928</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-7.242185731888206</v>
+        <v>-7.229142835593841</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.572533484248204</v>
+        <v>-5.559467229947728</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.9778269766194256</v>
+        <v>0.9910079859146634</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8375588744752065</v>
+        <v>-0.8243601355204433</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.687684059503091</v>
+        <v>-1.67427893185026</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.370720510916122</v>
+        <v>3.38417780462634</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.405103668261553</v>
+        <v>3.418555956981663</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.984849057316652</v>
+        <v>2.998405103668254</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.743342319417557</v>
+        <v>6.732912683719405</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>43</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.320515168162117</v>
+        <v>3.33303745783774</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.360104345895465</v>
+        <v>6.373014155471516</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.61639842999662</v>
+        <v>10.62940556141422</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.769907376557676</v>
+        <v>3.78288651895614</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.9059047661366009</v>
+        <v>0.9190155705115401</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.203346703852262</v>
+        <v>1.216389600146627</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.444194381928888</v>
+        <v>3.457260636229364</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6514295877984821</v>
+        <v>0.6646105970937199</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.735151693732597</v>
+        <v>-1.721952954777834</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.717048702634763</v>
+        <v>6.730453830287594</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.837876773666025</v>
+        <v>8.851334067376243</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.546678535662615</v>
+        <v>6.560130824382725</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.126423924717713</v>
+        <v>6.139979971069316</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.376145256994</v>
+        <v>6.365715621295848</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>41</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.165098265155883</v>
+        <v>1.177620554831506</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.431573432679421</v>
+        <v>4.444483242255473</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8413440544049635</v>
+        <v>-0.8283369229873614</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7110909217975419</v>
+        <v>-0.6981117793990776</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.688536527113541</v>
+        <v>-3.675425722738602</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-8.269143369885683</v>
+        <v>-8.256100473591317</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.40222047381765</v>
+        <v>1.415286728118126</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.813085855524015</v>
+        <v>5.826266864819253</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.313061579097678</v>
+        <v>3.326260318052441</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.462936394069892</v>
+        <v>2.476341521722723</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.697207459996207</v>
+        <v>4.710664753706425</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.146458163146157</v>
+        <v>-0.1330058744260469</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.872311616152764</v>
+        <v>1.885867662504367</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.756015832058743</v>
+        <v>-2.766445467756895</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.46952464275294</v>
+        <v>10.48204693242856</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.253160081322385</v>
+        <v>-2.240250271746334</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.648028787918975</v>
+        <v>-2.635021656501372</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>15.46232164813482</v>
+        <v>15.47543245250976</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11.97132616487445</v>
+        <v>11.98439241917492</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.096735358685599</v>
+        <v>4.109916367980837</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.73943917620705</v>
+        <v>7.752637915161813</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.684560666861543</v>
+        <v>6.698017960571761</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.015240120503222</v>
+        <v>3.028692409223332</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.00239291696582</v>
+        <v>10.01594896331743</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>13.95581795294576</v>
+        <v>13.94538831724761</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>31</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.106341546016381</v>
+        <v>-4.093819256340758</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.717915158980681</v>
+        <v>-5.70500534940463</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.886977413964374</v>
+        <v>-2.873970282546772</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.694888621868941</v>
+        <v>3.707867764267405</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.156467406796814</v>
+        <v>3.169578211171753</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.679715796125329</v>
+        <v>6.692758692419694</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.369175627240153</v>
+        <v>3.382241881540629</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.127798680071507</v>
+        <v>6.140979689366745</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>12.51841169711505</v>
+        <v>12.53161043606981</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.442480060474139</v>
+        <v>8.45588518812697</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.23772673615656</v>
+        <v>8.251184029866778</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.04630344188913</v>
+        <v>5.05975573060924</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.051370523894441</v>
+        <v>-5.037814477542838</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.801649191618154</v>
+        <v>-4.812078827316306</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>15</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-12.49343832020998</v>
+        <v>-12.48091603053435</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11.75861794443126</v>
+        <v>11.7717287488062</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.277273451186588</v>
+        <v>-1.264230554892222</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-15.22352378675591</v>
+        <v>-15.21032504780115</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-9.406982305117175</v>
+        <v>-9.393577177464344</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-9.611735629434754</v>
+        <v>-9.598278335724537</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.910685805422553</v>
+        <v>-2.897233516702443</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-16.66427374970098</v>
+        <v>-16.65071770334938</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.081219084091266</v>
+        <v>-3.091648719789418</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>27</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.34529017206188</v>
+        <v>-4.332767882386257</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.15424732608502</v>
+        <v>5.167157135661071</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-10.05543619532638</v>
+        <v>-10.04242906390878</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.59333545579964</v>
+        <v>8.606314598198104</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.054914240727364</v>
+        <v>8.068025045102303</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.352356178443188</v>
+        <v>8.365399074737553</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.563918757467142</v>
+        <v>4.576985011767619</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>15.14684658361445</v>
+        <v>15.16004532256922</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.29672139858653</v>
+        <v>14.31012652623936</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>21.49937548167637</v>
+        <v>21.51283277538658</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>21.53375863902174</v>
+        <v>21.54721092774185</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>21.1135040280769</v>
+        <v>21.1270600744285</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>17.65952165664942</v>
+        <v>17.64909202095127</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>9</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.062117235345738</v>
+        <v>3.074639525021361</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-9.660567488729789</v>
+        <v>-9.647657679153738</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.055674915784579</v>
+        <v>1.068682047202181</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-21.03629417382999</v>
+        <v>-21.02331503143153</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.647506833320378</v>
+        <v>0.6606176376953172</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.50414276609289</v>
+        <v>11.51732377538813</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.44314287991092</v>
+        <v>11.45634161886568</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>21.70412880599395</v>
+        <v>21.71753393364678</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6750112944803206</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>21.1135040280769</v>
+        <v>21.1270600744285</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.8589968618688886</v>
+        <v>-0.8694264975670407</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>15</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>25.50011936022928</v>
+        <v>25.51312649164688</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>18.96370582617006</v>
+        <v>18.97668496856853</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>25.09195127776441</v>
+        <v>25.10506208213935</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>25.38939321548027</v>
+        <v>25.40243611177463</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25.30465949820789</v>
+        <v>25.31772575250837</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>24.83747609942649</v>
+        <v>24.85065710872173</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>31.4431428799107</v>
+        <v>31.45634161886547</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>23.92635102821626</v>
+        <v>23.93975615586909</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>23.72159770389862</v>
+        <v>23.73505499760884</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>23.33572625029915</v>
+        <v>23.34928229665076</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>9.045023218251565</v>
+        <v>9.057545507927188</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>30.51037268221038</v>
+        <v>30.52328249178643</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>22.42319628330611</v>
+        <v>22.43620341472371</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>14.86114172360585</v>
+        <v>14.87412086600431</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>22.01502820084144</v>
+        <v>22.02813900521638</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22.31247013855699</v>
+        <v>22.32551303485135</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>22.22773642128487</v>
+        <v>22.24080267558534</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.37593763788793</v>
+        <v>6.389118647183167</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.00724544401326</v>
+        <v>14.02044418296802</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.15712025898533</v>
+        <v>13.17052538663816</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.432248449947629</v>
+        <v>-2.418791156237411</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.294442399705552</v>
+        <v>5.307894688425662</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.56649548106828</v>
+        <v>12.58005152741988</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.50852450565233</v>
+        <v>20.49809486995418</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4082</v>
+        <v>4083</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02641340570093575</v>
+        <v>-0.0267035763218928</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1583645632831363</v>
+        <v>0.1580200063480817</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02113597801998424</v>
+        <v>0.02082255810170608</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01805276660837762</v>
+        <v>0.01774068704354193</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1041762166398144</v>
+        <v>0.1038398870771218</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.04823400784993481</v>
+        <v>0.04791288439067642</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1236418856834263</v>
+        <v>0.1233016879449025</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1592279956828122</v>
+        <v>0.1588762868038245</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.06281982557888455</v>
+        <v>0.06249119883452181</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.08302177485018802</v>
+        <v>0.08268322390618721</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.04829213698268831</v>
+        <v>-0.03483484327247055</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.02462638655226357</v>
+        <v>-0.02493649507871964</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.05872404603753978</v>
+        <v>0.05839101359487842</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.02836771976305386</v>
+        <v>0.02860599488116833</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1735606827810443</v>
+        <v>0.1729588760193437</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2205926542104564</v>
+        <v>0.2199616849760915</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1135856943937625</v>
+        <v>0.1129769030155146</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2824054187533633</v>
+        <v>0.2817556252600824</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3065221360479384</v>
+        <v>0.3058602861803621</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2433987058719822</v>
+        <v>0.2427554730519788</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2971707313581646</v>
+        <v>0.2965128750439305</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2931564989270186</v>
+        <v>0.2924943528554209</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2460066827745564</v>
+        <v>0.2453553516994802</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1092138810765206</v>
+        <v>0.1085873247001601</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.09553944324105856</v>
+        <v>-0.08208214953084081</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1220801082712271</v>
+        <v>-0.1226477893314097</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.07842021308503888</v>
+        <v>-0.07900356042075884</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.03544758257540082</v>
+        <v>0.03590272568254704</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.2282585875334462</v>
+        <v>0.2273108473399432</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1383418500568538</v>
+        <v>0.1373893151955841</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.01253724933359734</v>
+        <v>-0.01345837542888972</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2851039506371862</v>
+        <v>0.2841084749180922</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2467223189515124</v>
+        <v>0.2457270437762773</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1232724375886605</v>
+        <v>0.1223133182212024</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1805233323517328</v>
+        <v>0.179547656295469</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1370152699333076</v>
+        <v>0.1360423147620651</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.06456840274472597</v>
+        <v>0.06361248420090249</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1197437221039337</v>
+        <v>-0.1063385944511026</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3757134356660856</v>
+        <v>-0.3622561419558679</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3013961879363123</v>
+        <v>-0.3022697949782582</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2205125403747275</v>
+        <v>-0.2214144246607646</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.08446528262193453</v>
+        <v>-0.08370611153934959</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.4727760985184091</v>
+        <v>0.4712116290401127</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2324015846544043</v>
+        <v>0.2308561099745816</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1302417657640405</v>
+        <v>0.1432488971816426</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5265938871953821</v>
+        <v>0.5395730295938463</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.348805150535334</v>
+        <v>0.3472121619691464</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2083495520083929</v>
+        <v>0.2068012967625563</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2713705501386485</v>
+        <v>0.2698024298246651</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2450413631450985</v>
+        <v>0.2434666959386647</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01435778622300887</v>
+        <v>-0.01586580432752527</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1184131604329153</v>
+        <v>-0.1050080327800842</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3764571855232219</v>
+        <v>-0.3629998918130042</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1939125289478838</v>
+        <v>-0.1953949875258871</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.03937372304133646</v>
+        <v>-0.04090960100386809</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.03878091590873112</v>
+        <v>0.03996062882872309</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3589</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1615519494591879</v>
+        <v>0.1594397226618725</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.0384808365699314</v>
+        <v>0.03633824337429559</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.02268375434256598</v>
+        <v>-0.009676622924963851</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5525081991770548</v>
+        <v>0.5654873415755191</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.4744269384042852</v>
+        <v>0.4721366093919528</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3420921581624157</v>
+        <v>0.3398491854880277</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3004847139050852</v>
+        <v>0.2982488465539959</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.3497255426335215</v>
+        <v>0.3474564407561331</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1092525986520556</v>
+        <v>0.1070468898380526</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.1003824722015523</v>
+        <v>-0.08697734454872119</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1937462114453368</v>
+        <v>-0.180288917735119</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.06017512761393107</v>
+        <v>-0.06236857657444261</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.01896865078754217</v>
+        <v>-0.02119124095374758</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1193010236453347</v>
+        <v>0.1088713879471825</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3396</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2990366944872633</v>
+        <v>0.2960454740204597</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.03268026601751473</v>
+        <v>-0.03566473382745272</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1629209220407404</v>
+        <v>-0.1499137906231383</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3789758447919809</v>
+        <v>0.3919549871904451</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2390101012939212</v>
+        <v>0.2359059515896078</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.02310901424450407</v>
+        <v>0.0200831705980633</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1015988743114846</v>
+        <v>0.09854364012237227</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1935679181432803</v>
+        <v>0.2067489274385181</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.001674917983564228</v>
+        <v>-0.001378608719342367</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2008200050484845</v>
+        <v>-0.1874148773956534</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3172601118211773</v>
+        <v>-0.3038028181109595</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.224001476112484</v>
+        <v>-0.2105491873923739</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.06827846112609137</v>
+        <v>-0.0713829962547905</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.004764425920512849</v>
+        <v>-0.005665209777639291</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3160</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5723012499543714</v>
+        <v>0.5680571132255139</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1472801945526072</v>
+        <v>0.1430432619896891</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2159729571909992</v>
+        <v>-0.2029658257733971</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.262051278799369</v>
+        <v>0.2750304211978332</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1978633865220161</v>
+        <v>0.2109741908969553</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.03834957221641133</v>
+        <v>0.03411489773722565</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1290821492676812</v>
+        <v>0.1248098764805405</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.05338122420537417</v>
+        <v>-0.04020021491013637</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1918782171356526</v>
+        <v>-0.1960890465357252</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.4407375793787764</v>
+        <v>-0.4273324517259454</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.455617485974841</v>
+        <v>-0.4421601922646232</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2313609109078882</v>
+        <v>-0.2179086221877782</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.0819952686882317</v>
+        <v>-0.0684392223366288</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1170840629942234</v>
+        <v>-0.1275136986923755</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>2900</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3991236632611006</v>
+        <v>0.3934385305671881</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.05747490251629017</v>
+        <v>-0.06317650376347217</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4523436091128801</v>
+        <v>-0.4393364776952779</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5046404914587939</v>
+        <v>0.5176196338572581</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4829261313642377</v>
+        <v>0.496036935739177</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.0620196032655258</v>
+        <v>-0.06776712625509163</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1478170300934423</v>
+        <v>0.1419848841417206</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.04359939178354466</v>
+        <v>-0.03041838248830686</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2580065453765954</v>
+        <v>-0.2637548995763979</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2460627648872915</v>
+        <v>-0.2326576372344604</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.2094367788600451</v>
+        <v>-0.1959794851498273</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.03184293020953533</v>
+        <v>0.04529521892964539</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.0598641813335874</v>
+        <v>0.0734202276851903</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1026889618857467</v>
+        <v>0.09225932618759458</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2571</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2465539067624363</v>
+        <v>0.2385866889683683</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2495759361881298</v>
+        <v>0.2413607601950574</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.282389966761059</v>
+        <v>0.2953970981786611</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.306888822541183</v>
+        <v>1.319867964939647</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.235030593472132</v>
+        <v>1.248141397847071</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7764021614156036</v>
+        <v>0.7679104508103052</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.769459187044923</v>
+        <v>0.782525441345399</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7690202456729835</v>
+        <v>0.7822012549682213</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6691249880398829</v>
+        <v>0.6823237269946461</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.10254706088827</v>
+        <v>1.115952188541101</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8977937365706907</v>
+        <v>0.9112510302809085</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.00996763681772</v>
+        <v>1.02341992553783</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8619806260284051</v>
+        <v>0.875536672380008</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.9950158439522951</v>
+        <v>0.984586208254143</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>2260</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3592817151725995</v>
+        <v>0.3484385229581264</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1427756774452362</v>
+        <v>0.1316926574721435</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4558715726185625</v>
+        <v>0.4688787040361646</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.117098156553496</v>
+        <v>1.13007729895196</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7556680919238019</v>
+        <v>0.7687788962987412</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6106321535332668</v>
+        <v>0.6236750498276322</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1719161353760299</v>
+        <v>0.1849823896765059</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5011929135856832</v>
+        <v>0.514373922880921</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4401930274033816</v>
+        <v>0.4533917663581448</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.005997045915272</v>
+        <v>1.019402173568103</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8454915092083155</v>
+        <v>0.8589488029185333</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.8798746665537465</v>
+        <v>0.8933269552738565</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6808589936619498</v>
+        <v>0.6944150400135527</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7535891754957476</v>
+        <v>0.7431595397975954</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1894</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9102556111884468</v>
+        <v>0.8946113956259865</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.224449524059132</v>
+        <v>0.2086894331300542</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1991689906409988</v>
+        <v>0.2121761220586009</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9102035382432234</v>
+        <v>0.9231826806416876</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.6357738754413802</v>
+        <v>0.6488846798163195</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5636276399785842</v>
+        <v>0.5766705362729496</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3732973017981678</v>
+        <v>0.3863635560986438</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7508868702817182</v>
+        <v>0.764067879576956</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.531492052737228</v>
+        <v>0.5446907916919912</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.265316181331258</v>
+        <v>1.278721308984089</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.060562857013679</v>
+        <v>1.074020150723896</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.517332497991639</v>
+        <v>1.530784786711749</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.149876197500795</v>
+        <v>1.163432243852398</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9772110461445678</v>
+        <v>0.9667814104464156</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1575</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.966879140107487</v>
+        <v>0.9454799085519383</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.006099177936882</v>
+        <v>1.019008987512933</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.182659042768854</v>
+        <v>1.195666174186456</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.757356619820804</v>
+        <v>1.770335762219268</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.282427468240698</v>
+        <v>1.295538272615637</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6909805170674659</v>
+        <v>0.7040234133618313</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.1141833077317</v>
+        <v>1.127249562032176</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.408904670854959</v>
+        <v>1.422085680150197</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9669524037202777</v>
+        <v>0.9801511426750409</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.339049440914579</v>
+        <v>2.35245456856741</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.070804053104929</v>
+        <v>2.084261346815147</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.359155464418613</v>
+        <v>2.372607753138723</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.875408789981648</v>
+        <v>1.888964836333251</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.807669804797619</v>
+        <v>1.797240169099467</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1292</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8347350544030334</v>
+        <v>0.8060135905019976</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.009539150417105</v>
+        <v>2.022448959993156</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.537271063015559</v>
+        <v>1.550278194433162</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.82232295723297</v>
+        <v>1.835302099631434</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.825697407795467</v>
+        <v>1.838808212170406</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.807349871826915</v>
+        <v>0.8203927681212804</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.187012439384361</v>
+        <v>1.200078693684837</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.339024087042489</v>
+        <v>1.352205096337727</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2718322503957893</v>
+        <v>0.2850309893505525</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.279292204686747</v>
+        <v>1.292697332339579</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.693733926808804</v>
+        <v>1.707191220519022</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.882915845764138</v>
+        <v>1.896368134484248</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.694859377234089</v>
+        <v>1.708415423585691</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.712382567095524</v>
+        <v>1.701952931397372</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1078</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.959251846765909</v>
+        <v>1.921308251207996</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.130609588161576</v>
+        <v>3.143519397737627</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.828505260043649</v>
+        <v>2.841512391461251</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.051522771129811</v>
+        <v>3.064501913528275</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.327572799100317</v>
+        <v>2.340683603475256</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.068428465943995</v>
+        <v>2.081471362238361</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.53691951315551</v>
+        <v>2.550100522450748</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.104862113058559</v>
+        <v>2.118060852013322</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.924495740646584</v>
+        <v>2.937900868299415</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.369093065679657</v>
+        <v>3.382550359389874</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.217947466067756</v>
+        <v>3.231399754787866</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.797692855122854</v>
+        <v>2.811248901474457</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.769121051963154</v>
+        <v>2.758691416265002</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>881</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.309058842105578</v>
+        <v>1.321581131781201</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.102706568528376</v>
+        <v>3.115616378104427</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.048359995870491</v>
+        <v>3.061367127288094</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.816524592723162</v>
+        <v>1.829503735121627</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.845640267548845</v>
+        <v>1.858751071923784</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.348530559407529</v>
+        <v>1.361573455701894</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.852900133849204</v>
+        <v>2.86596638814968</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.839746246985975</v>
+        <v>2.852927256281212</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.551731604844541</v>
+        <v>2.564930343799304</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.723172821632737</v>
+        <v>2.736577949285568</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.312971143172135</v>
+        <v>3.326428436882352</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.00683216657886</v>
+        <v>3.02028445529897</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.473070177654392</v>
+        <v>2.486626224005995</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.836298887910246</v>
+        <v>2.825869252212094</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>711</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.640176307075535</v>
+        <v>2.652698596751158</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.138307335461498</v>
+        <v>3.151217145037549</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.306026533224966</v>
+        <v>3.319033664642568</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.748515952752292</v>
+        <v>1.761495095150757</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.772682642040181</v>
+        <v>1.78579344641512</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.648183651485795</v>
+        <v>1.66122654778016</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.54797876684362</v>
+        <v>2.561045021144096</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.362089320242148</v>
+        <v>2.375270329537386</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.441736410149851</v>
+        <v>2.454935149104614</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.294846105572006</v>
+        <v>2.308251233224837</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.933974637794499</v>
+        <v>2.947431931504717</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.983828962509833</v>
+        <v>1.997281251229943</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.422927375474927</v>
+        <v>1.43648342182653</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.953942659931243</v>
+        <v>1.943513024233091</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>601</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.746162345347422</v>
+        <v>3.758684635023045</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.964871594280012</v>
+        <v>3.977781403856063</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.902781589846484</v>
+        <v>3.915788721264086</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.369141211638677</v>
+        <v>2.382120354037141</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.497941294403446</v>
+        <v>1.511052098778386</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.296215178874505</v>
+        <v>1.30925807516887</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.708985621336012</v>
+        <v>2.722051875636488</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.740970275799107</v>
+        <v>2.754151285094345</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.513581038535271</v>
+        <v>2.526779777490034</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.828181311078062</v>
+        <v>2.841586438730893</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.788153444331193</v>
+        <v>3.801610738041411</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.825864388698257</v>
+        <v>1.839316677418367</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.738388479916416</v>
+        <v>1.751944526268019</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.154499163274238</v>
+        <v>2.144069527576086</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>500</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.90656167979003</v>
+        <v>2.919083969465653</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.694988066825765</v>
+        <v>3.707897876401816</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.500119360229171</v>
+        <v>3.513126491646773</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.030372492836669</v>
+        <v>2.043351635235133</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.091951277764501</v>
+        <v>2.10506208213944</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.504659498207886</v>
+        <v>3.517725752508362</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.837476099426382</v>
+        <v>2.85065710872162</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.776476213244081</v>
+        <v>2.789674952198844</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.326351028216159</v>
+        <v>3.33975615586899</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.721597703898581</v>
+        <v>4.735054997608799</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.755980861244012</v>
+        <v>2.769433149964122</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.735726250299109</v>
+        <v>2.749282296650712</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.985447582575397</v>
+        <v>2.975017946877244</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>428</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.179458876051704</v>
+        <v>2.191981165727327</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.306203020096795</v>
+        <v>4.319112829672846</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.546848332191793</v>
+        <v>5.559855463609395</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.807942586294622</v>
+        <v>3.820921728693087</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.970455950661702</v>
+        <v>3.983566755036641</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.632383869685775</v>
+        <v>2.64542676598014</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.650453890731256</v>
+        <v>4.663520145031733</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.482335912510507</v>
+        <v>3.495516921805745</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.122270605767454</v>
+        <v>4.135469344722217</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.141304299244197</v>
+        <v>5.154709426897028</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.572064993618206</v>
+        <v>6.585522287328423</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.2699995528328</v>
+        <v>4.28345184155291</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.317034661514064</v>
+        <v>4.330590707865667</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.333111133977262</v>
+        <v>4.32268149827911</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>362</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.926451182552455</v>
+        <v>1.938973472228078</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.839739448041236</v>
+        <v>5.852649257617287</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.549843117135261</v>
+        <v>6.562850248552863</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.746394592284197</v>
+        <v>4.759373734682661</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.760459565057332</v>
+        <v>4.773570369432271</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.505415314927689</v>
+        <v>4.518458211222054</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.354383255113973</v>
+        <v>6.367449509414449</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.887199856332472</v>
+        <v>5.90038086562771</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.102443064072816</v>
+        <v>6.115641803027579</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.46226263042611</v>
+        <v>7.475667758078941</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.362481681799139</v>
+        <v>8.375938975509357</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.634433899918044</v>
+        <v>5.647886188638154</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.042908570741098</v>
+        <v>6.056464617092701</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.187657527326785</v>
+        <v>5.177227891628633</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>305</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.277053483068713</v>
+        <v>1.289575772744335</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.239250361907729</v>
+        <v>5.25216017148378</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.483725917606222</v>
+        <v>6.496733049023824</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.613979050213722</v>
+        <v>6.626958192612186</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>7.059164392518603</v>
+        <v>7.072275196893543</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.70086862531624</v>
+        <v>6.713911521610605</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.583348022798056</v>
+        <v>8.596414277098532</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.804689214180485</v>
+        <v>6.817870223475722</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.399427032916215</v>
+        <v>7.412625771870978</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.172252667560429</v>
+        <v>9.18565779521326</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.295368195701855</v>
+        <v>9.308825489412072</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.051062828457127</v>
+        <v>6.064515117177237</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.614414774889276</v>
+        <v>6.627970821240879</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.896922992411469</v>
+        <v>4.886493356713316</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>262</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.9416761836068162</v>
+        <v>0.9541984732824389</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.055293410337221</v>
+        <v>5.068203219913272</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.805462871679559</v>
+        <v>5.818470003097161</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.080754172225987</v>
+        <v>7.093733314624451</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.069050514405731</v>
+        <v>8.08216131878067</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.603133673495435</v>
+        <v>7.616176569789801</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.426796902788034</v>
+        <v>9.43986315708851</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.814575336067612</v>
+        <v>7.82775634536285</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.898613617824232</v>
+        <v>8.911812356778995</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.575205990048218</v>
+        <v>9.588611117701049</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.370452665730639</v>
+        <v>9.383909959440857</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.969721319259278</v>
+        <v>5.983173607979388</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.694504876253305</v>
+        <v>6.708060922604908</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.654149872651736</v>
+        <v>4.643720236953584</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>221</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.9002268381610676</v>
+        <v>0.9127491278366904</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.171006166373282</v>
+        <v>5.183915975949333</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.038580898690718</v>
+        <v>7.05158803010832</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.526300094646629</v>
+        <v>8.539279237045093</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>10.25032231848849</v>
+        <v>10.26343312286343</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>10.54776425620415</v>
+        <v>10.56080715249851</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.91551922671467</v>
+        <v>10.92858548101515</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.185892389019145</v>
+        <v>8.199073398314383</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.934847253968066</v>
+        <v>9.948045992922829</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.89467682007135</v>
+        <v>10.90808194772418</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.23743480797097</v>
+        <v>10.25089210168119</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.104397150836768</v>
+        <v>7.117849439556878</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.589119915457481</v>
+        <v>7.602675961809084</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.028886496602546</v>
+        <v>6.018456860904394</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>194</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4315826501068756</v>
+        <v>-0.4190603604312528</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.204266417341231</v>
+        <v>6.217176226917282</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.386717298373505</v>
+        <v>8.399724429791107</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.001506513455233</v>
+        <v>8.014485655853697</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>9.524940968486163</v>
+        <v>9.538051772861103</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>10.33784682372759</v>
+        <v>10.35088972002195</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10.76857702398109</v>
+        <v>10.78164327828156</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.755001872622259</v>
+        <v>8.768182881917497</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.24039373901729</v>
+        <v>10.25359247797205</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.93666030656667</v>
+        <v>10.9500654342195</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.73190698224909</v>
+        <v>10.7453642759593</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.673506634439882</v>
+        <v>7.686958923159992</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.25325202349498</v>
+        <v>7.266808069846583</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.925653768142411</v>
+        <v>4.915224132444258</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>163</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2672978761090405</v>
+        <v>0.2798201657846633</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.47167518339019</v>
+        <v>8.484584992966241</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.53079420685495</v>
+        <v>10.54380133827255</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.820556541916432</v>
+        <v>8.833535684314896</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10.73612305690561</v>
+        <v>10.74923386128055</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.03356499462127</v>
+        <v>11.04660789091564</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12.17582514237967</v>
+        <v>12.18889139668015</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.254654013536815</v>
+        <v>9.267835022832053</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.807151059869859</v>
+        <v>9.820349798824623</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.41101360490327</v>
+        <v>11.42441873255611</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.2062602805857</v>
+        <v>11.21971757429591</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.173158775354437</v>
+        <v>8.186611064074548</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>9.593394961955546</v>
+        <v>9.606951008307149</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.775631631655152</v>
+        <v>6.765201995957</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>148</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>1.573138023519704</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.732825904663606</v>
+        <v>8.745735714239657</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.36498422509405</v>
+        <v>10.37799135651165</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.468210330674516</v>
+        <v>8.48118947307298</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.63249181830504</v>
+        <v>10.64560262267998</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.28128510737207</v>
+        <v>12.29432800366644</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12.87222706577545</v>
+        <v>12.88529332007593</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.70234096429126</v>
+        <v>9.715521973586497</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12.34404378081165</v>
+        <v>12.35724251976642</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>13.52094562281076</v>
+        <v>13.53435075046359</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.31619229849318</v>
+        <v>13.3296495922034</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.296521401784545</v>
+        <v>9.309973690504656</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.25464516921803</v>
+        <v>12.26820121556963</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.774636771764591</v>
+        <v>7.764207136066439</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>121</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.878462506236311</v>
+        <v>2.890984795911933</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.531351703189401</v>
+        <v>9.544261512765452</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>14.92160696353497</v>
+        <v>14.93461409495257</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.440289848208579</v>
+        <v>8.453268990607043</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.20765375710336</v>
+        <v>11.2207645614783</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>13.15798825680248</v>
+        <v>13.17103115309685</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>14.72614710151368</v>
+        <v>14.73921335581416</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.300286016781762</v>
+        <v>9.313467026076999</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.71862497357467</v>
+        <v>11.73182371252943</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.34783863152195</v>
+        <v>13.36124375917478</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.4901927452209</v>
+        <v>11.50365003893111</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.565898216615913</v>
+        <v>6.579350505336024</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.27787501062969</v>
+        <v>10.2914310569813</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.568918656955567</v>
+        <v>5.558489021257415</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>112</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.863704536932886</v>
+        <v>2.876226826608509</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>11.0735594953972</v>
+        <v>11.08646930497325</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16.03583364594347</v>
+        <v>16.04884077736107</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.80894392140811</v>
+        <v>10.82192306380657</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>12.05623699205022</v>
+        <v>12.06934779642516</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>14.13939321548017</v>
+        <v>14.15243611177453</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14.94751664106503</v>
+        <v>14.9605828953655</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.123190385140681</v>
+        <v>9.136371394435919</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.7407619275298</v>
+        <v>11.75396066648456</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.67635102821616</v>
+        <v>12.68975615586899</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.57874056104144</v>
+        <v>11.59219785475166</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.148838004101151</v>
+        <v>7.162290292821261</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.40715482172768</v>
+        <v>9.420710868079283</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>6.075017946877246</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>97</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.145736937521981</v>
+        <v>2.158259227197604</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.84344167507319</v>
+        <v>10.85635148464924</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>14.57228430868278</v>
+        <v>14.58529144010038</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.547898266032547</v>
+        <v>9.560877408431011</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.04040488601193</v>
+        <v>10.05351569038687</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.39970249383067</v>
+        <v>12.41274539012504</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.34589661160995</v>
+        <v>13.35896286591043</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.693146202519173</v>
+        <v>6.706327211814411</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.694001986439957</v>
+        <v>8.707200725394721</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.93666030656667</v>
+        <v>10.9500654342195</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.700979147197543</v>
+        <v>9.714436440907761</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.642578799388339</v>
+        <v>6.656031088108449</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.25325202349498</v>
+        <v>7.266808069846583</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.441117685668182</v>
+        <v>5.43068804997003</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>13.35726221737204</v>
+        <v>13.37026934878964</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.725610588074773</v>
+        <v>8.738589730473237</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.187189373002603</v>
+        <v>8.200300177377542</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>10.86558369167065</v>
+        <v>10.87862658796502</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.742238004188295</v>
+        <v>6.755419013483532</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.57874056104144</v>
+        <v>11.59219785475166</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>6.851218956482107</v>
+        <v>6.864671245202217</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>6.430964345537205</v>
+        <v>6.444520391888808</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>3.109257106384923</v>
+        <v>3.098827470686771</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1461439603307255</v>
+        <v>-0.1330331559557862</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.257040450588846</v>
+        <v>1.270106704889322</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.450160552025686</v>
+        <v>3.463565679678517</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.986657944862444</v>
+        <v>9.211245473799281</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.816221825099433</v>
+        <v>8.829674113819543</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.781509382829228</v>
+        <v>4.795065429180831</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.031230715105515</v>
+        <v>5.020801079407363</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>165</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.69825759731841</v>
+        <v>-3.685735307642787</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.297783017511584</v>
+        <v>-2.284873207935533</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.8854228084455187</v>
+        <v>-0.8724156770279166</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.803377868857183</v>
+        <v>-2.790334972562817</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.490521224683675</v>
+        <v>-3.477454970383199</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.957704623465176</v>
+        <v>-3.944523614169938</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.211475593984822</v>
+        <v>-2.198276855030059</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.155266690866767</v>
+        <v>1.168671818519599</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.14584012814101</v>
+        <v>5.783247768693144</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.786283891547036</v>
+        <v>6.799736180267146</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.75996867454154</v>
+        <v>5.773524720893143</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.373326370454187</v>
+        <v>2.362896734756035</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>263</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.059476056059033</v>
+        <v>-3.04695376638341</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1427477822308347</v>
+        <v>-0.1298379726547836</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.349175964002761</v>
+        <v>1.362183095420363</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.671514299616156</v>
+        <v>-2.658535157217692</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.07786004299021</v>
+        <v>-2.064749238615271</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1063743475556365</v>
+        <v>0.1194172438500019</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3557178602826738</v>
+        <v>-0.3426516059821978</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.06818427793210446</v>
+        <v>-0.05500326863686666</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.380249798149748</v>
+        <v>1.393448537104511</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.153623755488887</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>7.980152836978434</v>
+        <v>7.750206512760315</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.873851583677471</v>
+        <v>6.887303872397581</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.693140698968314</v>
+        <v>5.706696745319917</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.281265073069697</v>
+        <v>3.270835437371545</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>415</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.044750969374654</v>
+        <v>-4.032228679699031</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.883054892601443</v>
+        <v>-0.8701450830253918</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4328949938378059</v>
+        <v>-0.5489260143198109</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.770107123470282</v>
+        <v>-3.878179465243328</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.150254957247476</v>
+        <v>-2.137144152872537</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.6537722521457354</v>
+        <v>-0.64072935585137</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9783141228952275</v>
+        <v>-0.9652478685947514</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.9658812147222946</v>
+        <v>-0.9527002054270568</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.611008587344806</v>
+        <v>1.624207326299569</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.580197182062314</v>
+        <v>2.452945604310244</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.926416981007016</v>
+        <v>4.792747305301113</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.274053150400647</v>
+        <v>3.287505439120757</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.889943117768986</v>
+        <v>1.903499164120589</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.9348451729368463</v>
+        <v>0.9244155372386942</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8583264441342422</v>
+        <v>-0.8458041544586195</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.6282066554660446</v>
+        <v>0.6411164650420957</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6725331533326226</v>
+        <v>0.5905791594608871</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.72886757624795</v>
+        <v>-2.804924226833826</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.231019361268302</v>
+        <v>-2.217908556893363</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.24273113685144</v>
+        <v>-1.229688240557074</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8093301390978098</v>
+        <v>-0.7962638847973338</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.27651353787931</v>
+        <v>-1.263332528584073</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3896022926914142</v>
+        <v>0.4028010316461774</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.711818156243837</v>
+        <v>1.625421095419945</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.300453856411586</v>
+        <v>2.212563648127826</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.468285887240548</v>
+        <v>1.481738175960658</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.221341501598936</v>
+        <v>1.234897547950538</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1826698047976194</v>
+        <v>0.2474616210540219</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.204778526395543</v>
+        <v>-1.192256236719921</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7918952833206205</v>
+        <v>0.8048050928966717</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.113022586035633</v>
+        <v>1.054363605048842</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.139653346956607</v>
+        <v>-1.19535804218421</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5152838643543518</v>
+        <v>-0.5021730599794125</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.5573518718109227</v>
+        <v>0.5703947681052881</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.343419188130369</v>
+        <v>0.356485442430845</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1819288164856445</v>
+        <v>-0.2397821677641545</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7920001459737165</v>
+        <v>0.8051988849284797</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.698371753604768</v>
+        <v>1.637039467641308</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.217058144884319</v>
+        <v>2.154744116779781</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.807928913192065</v>
+        <v>1.746086846462184</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.127934042506908</v>
+        <v>1.141490088858511</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6725737204167501</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.704483685101494</v>
+        <v>-1.691961395425871</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.03699990114529328</v>
+        <v>0.04990971072134442</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9788952733584964</v>
+        <v>0.9371896080175972</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.417058337202846</v>
+        <v>-0.4573393815466957</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2097302256974132</v>
+        <v>-0.2506691431569976</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3844476170627544</v>
+        <v>0.3974905133571198</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2008019314423066</v>
+        <v>0.2138681857427827</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.679060257842238</v>
+        <v>0.6370072570895857</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.21211977760052</v>
+        <v>1.225318516555284</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.003655289861349</v>
+        <v>1.95955813606701</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.01057531475449</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.35280310553398</v>
+        <v>1.30911568964666</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.8903982184899633</v>
+        <v>0.8467996750022522</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8988804183962955</v>
+        <v>0.9308827580104548</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8450866718583185</v>
+        <v>-0.8325643821826958</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5260712693375424</v>
+        <v>0.5389810789135936</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.273882125350937</v>
+        <v>1.24311079305965</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8318916581067199</v>
+        <v>-0.8609688675142664</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7774429000482428</v>
+        <v>-0.8068876033951469</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5428157174471195</v>
+        <v>0.5558586137414849</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1433691756272424</v>
+        <v>0.1564354299277184</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5067674380090708</v>
+        <v>0.4761488475099824</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.075688811669288</v>
+        <v>1.088887550624051</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.057950713007337</v>
+        <v>1.02637032909734</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.9771182086304435</v>
+        <v>0.9454568888617558</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4252784145194681</v>
+        <v>0.3940388281975657</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3657420480874265</v>
+        <v>0.3342862429806317</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.186238096409383</v>
+        <v>0.2100890369246429</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3439056099295996</v>
+        <v>-0.3313833202539769</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.08632034438917913</v>
+        <v>-0.07341053481312798</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2604791435114677</v>
+        <v>-0.2812660317177134</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.843114718641807</v>
+        <v>-1.862882778729947</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.724528122984559</v>
+        <v>-1.744594811185571</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9277104049942437</v>
+        <v>-0.9146675086998783</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8539913450150891</v>
+        <v>-0.8745339228973776</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.9125239005736105</v>
+        <v>-0.9332279631084859</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.6894399843794261</v>
+        <v>-0.7103250478011418</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.380282263398357</v>
+        <v>-1.401081867895861</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.049848758217891</v>
+        <v>-1.070952511777939</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.231487810435183</v>
+        <v>-1.252482942709641</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9902925584783233</v>
+        <v>-1.011619958988391</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.270261325831122</v>
+        <v>-1.252568260019309</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.3807622638719508</v>
+        <v>-0.368239974196328</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.09425775905320677</v>
+        <v>0.1071675686292579</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3767073621090233</v>
+        <v>-0.3919334979202489</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.105919935361754</v>
+        <v>-1.120740222802439</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6760738006053941</v>
+        <v>-0.6912825653801349</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4548305168773865</v>
+        <v>-0.4700821745368557</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1163749793794437</v>
+        <v>0.1007890039459056</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3221262030330578</v>
+        <v>-0.3376274101068191</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1973457762847062</v>
+        <v>-0.2129414789890092</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.8614960121190904</v>
+        <v>-0.876997770832574</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6704358390783582</v>
+        <v>-0.686107914910842</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.7117695320438742</v>
+        <v>-0.727422195947824</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.47329788401359</v>
+        <v>-0.4892074778642268</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.6140274830414043</v>
+        <v>-0.6012674676033427</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7194567170562323</v>
+        <v>-0.7069344273806095</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.0342784741845108</v>
+        <v>0.04718828376056194</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.03011727430194355</v>
+        <v>-0.04096899674568277</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5774311020778313</v>
+        <v>-0.5880243507420673</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3466452134635603</v>
+        <v>-0.35745435801838</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2446568064592753</v>
+        <v>-0.2554586250675754</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.0421359363838576</v>
+        <v>-0.05305090391988898</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.3974821790101544</v>
+        <v>-0.4083420133152416</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1707997094272571</v>
+        <v>-0.18177871490699</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.7769456750805404</v>
+        <v>-0.787836111266337</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6055790771040606</v>
+        <v>-0.6165933540395514</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9866500230498758</v>
+        <v>-0.9974973689452895</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.6783582567431381</v>
+        <v>-0.6894330575067826</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.5801182474554309</v>
+        <v>-0.5711088136861306</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5533691692303364</v>
+        <v>-0.5408468795547137</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.4155422944348004</v>
+        <v>-0.4232584816465916</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5975353879446033</v>
+        <v>-0.6052439925961082</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.9080890456248625</v>
+        <v>-0.915664127932871</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6179371408580394</v>
+        <v>-0.625707148629786</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2226160223951155</v>
+        <v>-0.2304996327425854</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.4404309908179087</v>
+        <v>-0.4482480735116496</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6555901563517352</v>
+        <v>-0.6633975697535419</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3487646345401103</v>
+        <v>-0.3567040924852733</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.177735324906422</v>
+        <v>-1.185484691915207</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.014229523251437</v>
+        <v>-1.022076845105161</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.190006793076975</v>
+        <v>-1.197786286981504</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.8943007662967943</v>
+        <v>-0.902260913225831</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8933168961890772</v>
+        <v>-0.8865798917950798</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.345136171907825</v>
+        <v>-0.3326138822322022</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.7254625397600165</v>
+        <v>-0.7310487625448232</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5817114303394817</v>
+        <v>-0.5873934390291282</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6755588287033802</v>
+        <v>-0.6811976019354589</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6748773134915638</v>
+        <v>-0.6805778762372441</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1850600993410723</v>
+        <v>-0.1909018479756313</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.320340501792117</v>
+        <v>-0.3261479024725418</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4212943069647253</v>
+        <v>-0.4271206690561442</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.09266801310510431</v>
+        <v>0.08665306960072172</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3558874146062223</v>
+        <v>-0.3618421763061264</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5412673865047566</v>
+        <v>-0.5471834452135838</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6266278344081613</v>
+        <v>-0.6325139988536748</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.5404045778150106</v>
+        <v>-0.546369877262336</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.584409709453837</v>
+        <v>-0.579470570868061</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.6547286427906158</v>
+        <v>-0.6422063531149931</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.9265672736066293</v>
+        <v>-0.9308118010175335</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.8846450038766989</v>
+        <v>-0.8889386906700949</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.9308157538536648</v>
+        <v>-0.9350860665079139</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6767825723646865</v>
+        <v>-0.6811826708473134</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.55567948241967</v>
+        <v>-0.5600961879670621</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6552629323027759</v>
+        <v>-0.6596571230974533</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7170017537905551</v>
+        <v>-0.721417875118064</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.534002441348413</v>
+        <v>-0.5384854099091285</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.8164506540872978</v>
+        <v>-0.820916547882625</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9709589304056223</v>
+        <v>-0.9753946950472994</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9186711296915675</v>
+        <v>-0.9231234843400813</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.770491366281199</v>
+        <v>-0.7750297784544955</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7942090419791867</v>
+        <v>-0.7902670272160179</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3248001643106733</v>
+        <v>-0.3280961396914108</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.6766138749218058</v>
+        <v>-0.6799092209594164</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.7214284394673243</v>
+        <v>-0.7247375860231173</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3623415326642387</v>
+        <v>-0.3657530688619701</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3681155306169046</v>
+        <v>-0.3715620830093158</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2059895305708608</v>
+        <v>-0.2094679270958011</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5780509241561376</v>
+        <v>-0.5814237007115537</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6032533838562841</v>
+        <v>-0.6066507004549138</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4956429719185778</v>
+        <v>-0.4990788471932461</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.538369166431039</v>
+        <v>-0.5418491953015803</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6958041823198542</v>
+        <v>-0.6992515717342656</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.6140739166013915</v>
+        <v>-0.6175458582500539</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4694487877526328</v>
+        <v>-0.4729940271472159</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5984744637096213</v>
+        <v>-0.5954538948274717</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.51766675978309</v>
+        <v>-0.5201317168088551</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4985491518701366</v>
+        <v>-0.5011012582967709</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5893467292369152</v>
+        <v>-0.5918937045447876</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2414519875328409</v>
+        <v>-0.2440942522107434</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2444622365294506</v>
+        <v>-0.247131913241617</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1911960392858632</v>
+        <v>-0.1938676710727094</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3468862978048222</v>
+        <v>-0.3495186149093144</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3359343051978882</v>
+        <v>-0.338594552647919</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.3232635959493209</v>
+        <v>-0.325931984217334</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.2899589775675295</v>
+        <v>-0.2926809646860846</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4207222266770643</v>
+        <v>-0.423418108232724</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2255006202374616</v>
+        <v>-0.2282527048232623</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1085573965894611</v>
+        <v>-0.1113658514974389</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.247789244292008</v>
+        <v>-0.2455319807638503</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3564</v>
+        <v>3565</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6063821278700203</v>
+        <v>-0.6083615308138377</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5255935886552194</v>
+        <v>-0.5276626491782821</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.5698107097008887</v>
+        <v>-0.5718846940355462</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2845687494688605</v>
+        <v>-0.2867182948347846</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1361483583955803</v>
+        <v>-0.1383626520519385</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.07533242841680732</v>
+        <v>-0.07755269315129709</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2848112382804899</v>
+        <v>-0.2869774949720352</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3165855252234664</v>
+        <v>-0.3187632217180294</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2501418870641245</v>
+        <v>-0.2523418545238343</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3001063708869793</v>
+        <v>-0.3023284616709319</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4611889515541847</v>
+        <v>-0.4633754956647422</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1307269346056756</v>
+        <v>-0.133005874426118</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1144841283825215</v>
+        <v>-0.1167861273537767</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2136545498600668</v>
+        <v>-0.2117983224074678</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3727205388070374</v>
+        <v>-0.3743653374112199</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3655504156327538</v>
+        <v>-0.3672516613904619</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3921548508698365</v>
+        <v>-0.3938629018805528</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1655458745102649</v>
+        <v>-0.167312129726767</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1720661419415279</v>
+        <v>-0.1738494824863963</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.05030185666794296</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3108089113781674</v>
+        <v>-0.3125492270723527</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2456075290127231</v>
+        <v>-0.2473821069646434</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2098998085542831</v>
+        <v>-0.2116870744968722</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2818800974311557</v>
+        <v>-0.2836770866378231</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4714230158396902</v>
+        <v>-0.4731761280385172</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2036591714802896</v>
+        <v>-0.2054850615953114</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1994619657401699</v>
+        <v>-0.2013040136847124</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.261755691640154</v>
+        <v>-0.2602248245357401</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3737</v>
+        <v>3738</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2267716535433166</v>
+        <v>-0.2281834258955868</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3573458888957575</v>
+        <v>-0.3587687902648469</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5511079610088174</v>
+        <v>-0.5524910063526889</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3263929194931805</v>
+        <v>-0.327832996568489</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3431795284287631</v>
+        <v>-0.3446310056641337</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1646788806480046</v>
+        <v>-0.1661704018399845</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3684174248690368</v>
+        <v>-0.3698576920844303</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2600392625827013</v>
+        <v>-0.2615223784578546</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3063671860076482</v>
+        <v>-0.3078404098102396</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4200804072289088</v>
+        <v>-0.4215479595772962</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5832151303260105</v>
+        <v>-0.5846456172000813</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3199752767608004</v>
+        <v>-0.3214759409449712</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.323984825142297</v>
+        <v>-0.3254970561174062</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3535409108685457</v>
+        <v>-0.3522158679970246</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1611532049060003</v>
+        <v>-0.1623412335733931</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4221810026368829</v>
+        <v>-0.4233390208728096</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5407825799910597</v>
+        <v>-0.5419193799128479</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3439259598252633</v>
+        <v>-0.345111920087362</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3435156687202721</v>
+        <v>-0.3447149962764939</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2941544098150288</v>
+        <v>-0.2953603205444608</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4433719978551025</v>
+        <v>-0.4445413689820512</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4237473187936232</v>
+        <v>-0.4249334424594693</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4178515178483408</v>
+        <v>-0.4190412462784465</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5443608183822164</v>
+        <v>-0.5455379617780665</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6294269939469288</v>
+        <v>-0.6305872403738633</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3701689416469236</v>
+        <v>-0.3713971180337765</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.4077017202581956</v>
+        <v>-0.4089305811416679</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3535479472694618</v>
+        <v>-0.3524268480754387</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0792890818934211</v>
+        <v>-0.08029651582087638</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2826978835874598</v>
+        <v>-0.2836848759865092</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4311645457382696</v>
+        <v>-0.4321214422375093</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4161391350702957</v>
+        <v>-0.4170978610190517</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4495323097257966</v>
+        <v>-0.4504934734161097</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3965426686977054</v>
+        <v>-0.3975121952815499</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5189763952495667</v>
+        <v>-0.5199164398390934</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4030826175937818</v>
+        <v>-0.4040623120179561</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4240412511802276</v>
+        <v>-0.4250172361094755</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.561226611535389</v>
+        <v>-0.5621843357222147</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5704033315660837</v>
+        <v>-0.5713632218528986</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3144489678600877</v>
+        <v>-0.3154749525468787</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3576174430445818</v>
+        <v>-0.3586410591234994</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2487493086163113</v>
+        <v>-0.2478258759665835</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3903</v>
+        <v>3904</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.04195721704347477</v>
+        <v>-0.04282565524714954</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2097373482444809</v>
+        <v>-0.2105903769178923</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3097937721162509</v>
+        <v>-0.3106282976252501</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3701386239535083</v>
+        <v>-0.3709559784592855</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4346335893111615</v>
+        <v>-0.4354439234828362</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3789524761588012</v>
+        <v>-0.3797724771825202</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4753916526872501</v>
+        <v>-0.4761888473382214</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3914827135692676</v>
+        <v>-0.3923096431965263</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4384674919759703</v>
+        <v>-0.4392838607968059</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4811227368209501</v>
+        <v>-0.481942922943702</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.4668303554972226</v>
+        <v>-0.4676580814800175</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2388974998315305</v>
+        <v>-0.2397834398976357</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2861999792090941</v>
+        <v>-0.2870813397129268</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1757617435839691</v>
+        <v>-0.1749820531227542</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3944</v>
+        <v>3945</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0294504506117903</v>
+        <v>-0.03018333725491829</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1616347845392454</v>
+        <v>-0.1623573674697951</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3153041543093806</v>
+        <v>-0.3159938319123654</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3736740423175959</v>
+        <v>-0.37434747980911</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4683826458378206</v>
+        <v>-0.4690400928731933</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4608092136696342</v>
+        <v>-0.4614647230344673</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4559074468693041</v>
+        <v>-0.4565657454673371</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.3270808625989261</v>
+        <v>-0.3277787303064699</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3995177092679398</v>
+        <v>-0.4001984655226636</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4505486678324715</v>
+        <v>-0.4512289036397448</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.413188209453331</v>
+        <v>-0.4138811726039719</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2379370302917181</v>
+        <v>-0.2386742733953895</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2637667788517177</v>
+        <v>-0.264503815868288</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.2025848717856604</v>
+        <v>-0.201914879485237</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3971</v>
+        <v>3972</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04170224203902251</v>
+        <v>0.04104130949074403</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1758128370155561</v>
+        <v>-0.1764394729957672</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3311212223926248</v>
+        <v>-0.3317140807860639</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2877385345433794</v>
+        <v>-0.2883409815403439</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3603100287681542</v>
+        <v>-0.3609012436580983</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3758744397095768</v>
+        <v>-0.3764583605872716</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3715597074230814</v>
+        <v>-0.3721460745838669</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2970474107571661</v>
+        <v>-0.2976586278293993</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3442481328323694</v>
+        <v>-0.3448485579847045</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3755357642366661</v>
+        <v>-0.3761392163644146</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3649649533736863</v>
+        <v>-0.3655739332088075</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2158288543361522</v>
+        <v>-0.2164752546659727</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1939817053907262</v>
+        <v>-0.1946391732712627</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1063177158381023</v>
+        <v>-0.1057474106252698</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.009675004821161792</v>
+        <v>0.009123810103098151</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2186143248035251</v>
+        <v>-0.2191257848684174</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3508649407925049</v>
+        <v>-0.3513478481638899</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2569654932052003</v>
+        <v>-0.2574706922006911</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3331297494107517</v>
+        <v>-0.3336218660160881</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3213299765397863</v>
+        <v>-0.3218221779287802</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3426340912159063</v>
+        <v>-0.3431221277908847</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2473542398949675</v>
+        <v>-0.2478712025779544</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2447366642203477</v>
+        <v>-0.2452551875217139</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3072984974952746</v>
+        <v>-0.3078106023042011</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2983773273124086</v>
+        <v>-0.2988940787766268</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1750880698249162</v>
+        <v>-0.1756355142056591</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2315982563209218</v>
+        <v>-0.2321362847678685</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.142688349458588</v>
+        <v>-0.1421941440545567</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4017</v>
+        <v>4018</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.03686263782783783</v>
+        <v>-0.03735363906821476</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1958533330253118</v>
+        <v>-0.1963204858810599</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.30425005387211</v>
+        <v>-0.3046943075589752</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2102036184123861</v>
+        <v>-0.2106702118353638</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2880785284948075</v>
+        <v>-0.2885311634528094</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.3253333864867685</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3215830465237204</v>
+        <v>-0.3220258002866601</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2283951409414939</v>
+        <v>-0.2288657541014345</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.3005998683073798</v>
+        <v>-0.3010533600059659</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3412440973744921</v>
+        <v>-0.3416958580544218</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3331286642606202</v>
+        <v>-0.3335846442713262</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1852980638617296</v>
+        <v>-0.1857907306328954</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.292944730288248</v>
+        <v>-0.2934148917046002</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1536612050770856</v>
+        <v>-0.1532050496384301</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.06553592928071339</v>
+        <v>-0.06593328041113722</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1602387576318307</v>
+        <v>-0.1606256631594363</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3691778037658935</v>
+        <v>-0.3695165063808332</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1515712664134412</v>
+        <v>-0.1519627913986383</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2324997461683793</v>
+        <v>-0.2328757570317492</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2670727272641571</v>
+        <v>-0.2674380555089613</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2890210744902149</v>
+        <v>-0.2893818486762356</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1501782215612693</v>
+        <v>-0.1505771544232815</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1975914577857978</v>
+        <v>-0.1979793687888076</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2436094460921367</v>
+        <v>-0.2439929179763993</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1874707418637058</v>
+        <v>-0.1878699035769671</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.04036120499424811</v>
+        <v>-0.04079664988761778</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1500586693547845</v>
+        <v>-0.1504705456626851</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.03473045896762272</v>
+        <v>-0.03437636709061564</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.05861293899993569</v>
+        <v>-0.05898340206127273</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1812726957818569</v>
+        <v>-0.1816249962002416</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3660223720542817</v>
+        <v>-0.3663323029411671</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.197833266454488</v>
+        <v>-0.1981837978357248</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2305499531562205</v>
+        <v>-0.2308965691034786</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2643866416978682</v>
+        <v>-0.2647229231836121</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2618429648463021</v>
+        <v>-0.2621806744800566</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1243371550697958</v>
+        <v>-0.124712349406451</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1717741563961326</v>
+        <v>-0.1721383022973342</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1949208475541155</v>
+        <v>-0.1952857366889234</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1640038740106888</v>
+        <v>-0.1643780810207218</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.04179965663514906</v>
+        <v>-0.04220393090372454</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1028529307566401</v>
+        <v>-0.1032454468758033</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.03656080627236946</v>
+        <v>-0.03623020309808567</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4068</v>
+        <v>4069</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.03080661229524395</v>
+        <v>-0.03113651069114098</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1344236978801163</v>
+        <v>-0.1347387322725311</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2709029491603729</v>
+        <v>-0.2711872338434205</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1273518818567965</v>
+        <v>-0.1276706741544089</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1373840177959522</v>
+        <v>-0.1377039796555479</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1699787177877425</v>
+        <v>-0.1702889311491873</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1677331398289184</v>
+        <v>-0.1680446105927089</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.03243062615043613</v>
+        <v>-0.03277847410046064</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.05534308457079362</v>
+        <v>-0.05568587254341395</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1060654747307979</v>
+        <v>-0.1064014675044476</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.07599502516061563</v>
+        <v>-0.07633989433618638</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.003232897969745352</v>
+        <v>-0.003595589903234497</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.01644873126883795</v>
+        <v>-0.01681106944264599</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.001376786115223183</v>
+        <v>0.001658399076809758</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.001987416448372414</v>
+        <v>-0.002283551901868464</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03709109271491684</v>
+        <v>-0.03738790767243216</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1988053709536217</v>
+        <v>-0.1990650548961028</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.07972283837818139</v>
+        <v>-0.0800110236113909</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.06697292761445794</v>
+        <v>-0.06726742164935473</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.09850113521682147</v>
+        <v>-0.09878638211299062</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.0965146700895616</v>
+        <v>-0.09680102665524259</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.01204677798980214</v>
+        <v>-0.01235658990851363</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.01060161348132027</v>
+        <v>-0.01091227559660268</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.06385705011921061</v>
+        <v>-0.06415965421422243</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.08349534213472509</v>
+        <v>-0.08379445159561527</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.01363454725920121</v>
+        <v>0.01331170040486285</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.023624339471084</v>
+        <v>0.02329650189195576</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.06670217703753423</v>
+        <v>0.06693367446176524</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volume/volume_ratio_14.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_14.xlsx
@@ -568,53 +568,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.5107</t>
+          <t>X ≈ 0.5108</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-9.76877030580097</v>
+        <v>-9.795520941239396</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-2.86428067890418</v>
+        <v>-2.864734503660735</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.475635173607387</v>
+        <v>-4.474698263355243</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-12.86425648130241</v>
+        <v>-12.86161821792738</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.753277391118722</v>
+        <v>-9.702440358640132</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.458979764802976</v>
+        <v>-9.432747326507318</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.328136843557644</v>
+        <v>-8.278139512497368</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.3607076433481</v>
+        <v>-6.309933301386621</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8.859941430588378</v>
+        <v>-8.784578385464592</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.181247352638991</v>
+        <v>-1.081689126310572</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.270487990138797</v>
+        <v>2.36974820839086</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.742659703763302</v>
+        <v>4.866306029126179</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.762240899406322</v>
+        <v>6.91090009768979</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3274210775124473</v>
+        <v>-0.1554223179463321</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.991691573616137</v>
+        <v>-2.05301998818608</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.508532697764892</v>
+        <v>3.387245641953861</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.148455390449392</v>
+        <v>5.004754647071692</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1880497863289179</v>
+        <v>1.103031671849216</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.700758705600272</v>
+        <v>3.629488706480927</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.039548639424815</v>
+        <v>5.926468856646125</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.954831740097319</v>
+        <v>5.865124903681718</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.523436237328987</v>
+        <v>6.958153115566461</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.483543227688877</v>
+        <v>7.479942994891445</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.668341023143157</v>
+        <v>8.676802338572458</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.0762759365393</v>
+        <v>10.49351633462241</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.031073517195601</v>
+        <v>6.516002903157272</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.592727083750333</v>
+        <v>5.112808274354343</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.79950774279515</v>
+        <v>4.353077312504048</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.791582785274258</v>
+        <v>-5.434908944299998</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.169149811225509</v>
+        <v>-2.139174110416896</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.880622714653391</v>
+        <v>-3.828533977914709</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.020151686850021</v>
+        <v>-6.291248126731183</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.258685313733224</v>
+        <v>-2.892544801783117</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.962649889072402</v>
+        <v>-2.621214416822106</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.047726393099154</v>
+        <v>-2.682438663626364</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.51493698651052</v>
+        <v>-3.147694748994432</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.024948407030699</v>
+        <v>1.354713596720408</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1391737051617028</v>
+        <v>-0.7653970138913664</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3439021569946945</v>
+        <v>-0.9697402707412124</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.939686918358696</v>
+        <v>-3.507750695370618</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.675845961088569</v>
+        <v>-5.20199649955687</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.135508368911921</v>
+        <v>-3.655580696153194</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>162</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.378306517876545</v>
+        <v>7.347285117493499</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.540267364471212</v>
+        <v>4.536717255578857</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.531209956827425</v>
+        <v>3.529195327510145</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.03454095622215192</v>
+        <v>-0.0349014118231068</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.420404145441303</v>
+        <v>-2.371965051870497</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.740784336791201</v>
+        <v>-2.716873514485464</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3604086173457404</v>
+        <v>-0.3124667841209217</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.060355490171972</v>
+        <v>-2.010525964055375</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.738913084329276</v>
+        <v>-2.664220613759682</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5044656874860891</v>
+        <v>-0.404986541873555</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.410837459501309</v>
+        <v>-4.309863890357413</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.142504795579882</v>
+        <v>-3.018854574278208</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4777564789044249</v>
+        <v>-0.3290964753762111</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.486710448184482</v>
+        <v>-1.931995639235105</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.24425525979278</v>
+        <v>-2.246648448098988</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.303292184188415</v>
+        <v>1.287654199092678</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.457916234603616</v>
+        <v>2.429601728261773</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.618937473656793</v>
+        <v>3.584446882289484</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.628816992276839</v>
+        <v>4.632217902947623</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.966405592567433</v>
+        <v>5.929353950519456</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.812232686148811</v>
+        <v>3.822090408415477</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.82332543156766</v>
+        <v>2.844964515902106</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.014886232329857</v>
+        <v>1.783571155020958</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.680306912177656</v>
+        <v>1.473183579560676</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.993043754163168</v>
+        <v>1.78197725901606</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.544995953672661</v>
+        <v>2.353272508981128</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.8619756036179353</v>
+        <v>0.4209300857697116</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.124240744804702</v>
+        <v>1.695734655161971</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.34614427126764</v>
+        <v>-3.338975845886118</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.428534508328205</v>
+        <v>-2.405116733862002</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5604439681684639</v>
+        <v>0.5529985566365738</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.957555108108544</v>
+        <v>1.941429715201693</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5697380015420777</v>
+        <v>0.6149407444482335</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1677992775365098</v>
+        <v>-0.3711839894026525</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2531568128090029</v>
+        <v>-0.431752868826365</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.513356087700252</v>
+        <v>3.298390368798366</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.605761151872962</v>
+        <v>2.422176221750256</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.025040778891267</v>
+        <v>2.858814470792602</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.54877897140409</v>
+        <v>1.39641697964116</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1120076028438106</v>
+        <v>-0.2244741416357101</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1107996300742471</v>
+        <v>-0.1994459405596061</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.625865404504367</v>
+        <v>1.310041916527751</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>260</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.515725919799117</v>
+        <v>2.483272321233436</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.443186803082682</v>
+        <v>2.437278461241462</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.433476061047543</v>
+        <v>2.427904403001975</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.430772335388106</v>
+        <v>-2.426654276849142</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.968571809266308</v>
+        <v>-2.915799717003267</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.170491319189999</v>
+        <v>1.193259928316991</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.06675751666342933</v>
+        <v>-0.01861827373906522</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1493052688460352</v>
+        <v>-0.09995421693984241</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5586454681486828</v>
+        <v>0.6308185103154784</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.598705382592549</v>
+        <v>-2.496452575210455</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.188021925468036</v>
+        <v>-3.085323206894451</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.15364377311289</v>
+        <v>-3.027965160266511</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.650717703349201</v>
+        <v>-1.501507926270008</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.578828206968907</v>
+        <v>-2.406829447402245</v>
       </c>
     </row>
     <row r="13">
@@ -936,257 +936,257 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.60354213163275</v>
+        <v>1.70612865586606</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.44301025950022</v>
+        <v>-2.284999314786099</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.1809778867284</v>
+        <v>-6.128734078467886</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.751621883506857</v>
+        <v>-5.697371445027066</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.381350821341087</v>
+        <v>-5.283876949245901</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-6.598244483808699</v>
+        <v>-6.522261469354902</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.863576734614036</v>
+        <v>-4.77575269272203</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.380707403463155</v>
+        <v>-6.447099478872715</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7.65697115767415</v>
+        <v>-7.690520204844617</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-10.77149004473891</v>
+        <v>-10.92910312622625</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-8.848531628531092</v>
+        <v>-9.024767856307726</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-7.598348005051008</v>
+        <v>-7.762382723889765</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.1947906516777</v>
+        <v>-6.348446483215362</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.88090910479449</v>
+        <v>-7.008270302619472</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.9251</t>
+          <t>X ≈ 0.925</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.559693519445922</v>
+        <v>-0.5838282898834137</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.038305815351954</v>
+        <v>1.031710591369759</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9652730922971173</v>
+        <v>-0.9563907495907316</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.699054155075167</v>
+        <v>2.689227845558662</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.731611666333372</v>
+        <v>4.75803982162536</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.816051949912691</v>
+        <v>1.833850452784269</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.124799707492294</v>
+        <v>4.971845858429113</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.728470613544779</v>
+        <v>2.588294981760079</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.345945048661875</v>
+        <v>2.231431424094325</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.817569660692143</v>
+        <v>1.73044041278316</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.291325094071823</v>
+        <v>1.206483827214576</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.968790063147395</v>
+        <v>1.905254692931635</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.19172602655425</v>
+        <v>2.151299507741889</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.739005085140988</v>
+        <v>2.72137568080295</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.977</t>
+          <t>X ≈ 0.9769</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>366</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.47793147931764</v>
+        <v>-2.496667811386907</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.266755137872309</v>
+        <v>-0.2663373248763321</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.79727949711139</v>
+        <v>1.790854853806543</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.20072868441553</v>
+        <v>2.195649523624667</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.389215087603922</v>
+        <v>1.435168351531324</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8669169860914678</v>
+        <v>0.8900626047389011</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.8571376354697193</v>
+        <v>-0.8064685039410904</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7777581918247591</v>
+        <v>-0.7250832874517457</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.01906821720011465</v>
+        <v>0.05545806675715426</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3225389260982254</v>
+        <v>-0.220389845500911</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.2540160406425684</v>
+        <v>-0.1523279063924647</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.405430238014013</v>
+        <v>-2.278260559563115</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.73268491646391</v>
+        <v>-1.582727961178861</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4140530913742495</v>
+        <v>-0.2420543318075872</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 1.029</t>
+          <t>X ≈ 1.028</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>319</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6434580794555487</v>
+        <v>0.615399692117002</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.792104604967271</v>
+        <v>-3.773107576747556</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.64361332026548</v>
+        <v>-4.789823007765712</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.259469681379279</v>
+        <v>-3.414010049779009</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.54384073917717</v>
+        <v>-2.656702748441653</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.05210934277087631</v>
+        <v>-0.1985754132571316</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.271615940281677</v>
+        <v>-3.386505783863129</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.484766088770606</v>
+        <v>-2.602127937543763</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.605309373819892</v>
+        <v>-1.700950264296679</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.022626289272111</v>
+        <v>-4.092585617817257</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.913847823707819</v>
+        <v>-3.987159508204208</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.625551176054685</v>
+        <v>-2.680152007971834</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.418742781719267</v>
+        <v>-2.451193174884779</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.133446002965947</v>
+        <v>-2.961447243399284</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 1.081</t>
+          <t>X ≈ 1.08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.582195395903604</v>
+        <v>1.41547730831018</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.562066787909174</v>
+        <v>-4.062066923170626</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4232692680705696</v>
+        <v>-0.9024252526098309</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.47374032781461</v>
+        <v>1.004163098296715</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.184690568037226</v>
+        <v>-1.618780629230976</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1727541329759035</v>
+        <v>-0.28392780352128</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7947575546285037</v>
+        <v>0.7242279837381602</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.741116472679231</v>
+        <v>1.685102862738368</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.153632549371999</v>
+        <v>4.139261932327457</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>7.190639548095177</v>
+        <v>6.886010392644749</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.80572637570063</v>
+        <v>3.475906794875428</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.546818308974721</v>
+        <v>4.248939525332162</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.713239893823904</v>
+        <v>2.783686130142826</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.23226176313166</v>
+        <v>1.961302420729623</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.8121529713722</v>
+        <v>-4.573854284756287</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.624812403971966</v>
+        <v>-2.931937808768815</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.954163227979386</v>
+        <v>-3.785654652550363</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.356648364764801</v>
+        <v>-3.200304375035515</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6893304412250458</v>
+        <v>0.4531532629227328</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.532143327477854</v>
+        <v>-4.34807028536482</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.14956396711775</v>
+        <v>-4.612511338597173</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.682053171652157</v>
+        <v>-4.153279060512723</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-8.948642804810497</v>
+        <v>-8.345225273181406</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.994823283383347</v>
+        <v>-5.940176457544943</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.732234722017317</v>
+        <v>-5.687881232306736</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.828697691157323</v>
+        <v>-3.786554156762548</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.846979385592277</v>
+        <v>-3.261287414830711</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.621243735365745</v>
+        <v>-2.54927958985234</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.603336638086262</v>
+        <v>4.789099605173533</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.268303967772383</v>
+        <v>3.193607388869836</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.858304156621401</v>
+        <v>1.285200487928883</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8.587514071783396</v>
+        <v>7.982286412571426</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.495925026301883</v>
+        <v>3.959573270540147</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.300913269134966</v>
+        <v>4.521456808253276</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.647674991086987</v>
+        <v>-0.09301125740093141</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.195834773696212</v>
+        <v>0.451864126167898</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1196241907775288</v>
+        <v>-0.5962789827000705</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.838233313229345</v>
+        <v>3.130365732996331</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.63353215496921</v>
+        <v>3.430642978607118</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.175524520522437</v>
+        <v>3.997472692594172</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.262987880406996</v>
+        <v>3.90406321498692</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.458266677841713</v>
+        <v>2.630265437408319</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>170</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.245621912887295</v>
+        <v>-4.820307416805818</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.966721405813544</v>
+        <v>2.382099705729978</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.98371472694086</v>
+        <v>1.991506475339676</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.113939870529222</v>
+        <v>2.111976588811991</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.163885611551208</v>
+        <v>2.21054906682231</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1083184647157509</v>
+        <v>0.137895378786375</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.141255164273041</v>
+        <v>4.184246937944401</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4.850657108721556</v>
+        <v>4.892319036411017</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.024969069845916</v>
+        <v>3.09709670092878</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.527991449986665</v>
+        <v>4.622712490378063</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.911525585844096</v>
+        <v>5.009338851342498</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7.298844914669999</v>
+        <v>7.422541535698244</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6.878694061356562</v>
+        <v>7.02738360913439</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6.516194417465449</v>
+        <v>6.099957882914495</v>
       </c>
     </row>
     <row r="21">
@@ -1352,101 +1352,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.390006939625209</v>
+        <v>-2.913692836612476</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.364829396325405</v>
+        <v>-0.9057378808248231</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.05858103710137641</v>
+        <v>0.4920625519196236</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.629375637492139</v>
+        <v>-1.184207236264136</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.286880263957627</v>
+        <v>3.701959298600919</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.584254293592771</v>
+        <v>3.974050147850946</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.681362116144783</v>
+        <v>2.125404290503283</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3052025632671302</v>
+        <v>0.7652293112744104</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.062402224926124</v>
+        <v>2.521803826810668</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6056983895855055</v>
+        <v>-0.09612669445288446</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>-1.202819829916308</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.860342240873216</v>
+        <v>3.352589230451827</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.28708133971287</v>
+        <v>0.2547286011853487</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8477452196045689</v>
+        <v>1.404674364101567</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 1.34</t>
+          <t>X ≈ 1.339</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>101</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>7.91512357342593</v>
+        <v>8.282714275261874</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.313838470461221</v>
+        <v>5.713872852809565</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>5.909166095607226</v>
+        <v>6.301753535555726</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.059193219393613</v>
+        <v>4.474643448182093</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.429591383207026</v>
+        <v>-1.365177781851379</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8479806662298657</v>
+        <v>0.8750079778408093</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.216927712838107</v>
+        <v>-1.14514873012309</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.276399682979104</v>
+        <v>2.329743707841239</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.225318516555348</v>
+        <v>1.307589799117451</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.375399720225424</v>
+        <v>0.4851155676549155</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8194004479357488</v>
+        <v>-0.7101364322543589</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.765220315382408</v>
+        <v>-2.641523694354163</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.185371168695816</v>
+        <v>-3.036681620917989</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.969536508568297</v>
+        <v>-1.797537749001634</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>72</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7.241306191687947</v>
+        <v>7.797450875367254</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.07456454306848315</v>
+        <v>0.6811221433705938</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-8.65354017501997</v>
+        <v>-7.989300025534021</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-8.523315031431608</v>
+        <v>-8.451217235313202</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-9.061604584527302</v>
+        <v>-8.93769875922942</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.98645277711428</v>
+        <v>-5.910621768309838</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.293385358602826</v>
+        <v>-3.197613066185525</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9826762246118221</v>
+        <v>-0.9050029289147972</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.210325047801227</v>
+        <v>-5.079639884532767</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.449132733019901</v>
+        <v>-7.298852189693008</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.139214485460229</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.036093164233783</v>
+        <v>-4.864094404667121</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>66</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.579690030071703</v>
+        <v>3.537867571787636</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.025590343472594</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.05858103710127693</v>
+        <v>0.1021153264201899</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.326345334461877</v>
+        <v>-1.285954862393851</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3494833724060555</v>
+        <v>-0.2686917845683539</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.627866918528539</v>
+        <v>-7.518932350260435</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-4.682274247491677</v>
+        <v>-4.557028992555026</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-9.694797436732919</v>
+        <v>-9.534770401769805</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-6.725476562952664</v>
+        <v>-6.560625575226858</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-7.575395359282567</v>
+        <v>-7.405111218865017</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.23464197208817</v>
+        <v>-3.10744258646406</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.200263819732847</v>
+        <v>-3.076567198704602</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.135566188197771</v>
+        <v>-4.986876640419943</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3643759925168197</v>
+        <v>-0.1923772329501574</v>
       </c>
     </row>
     <row r="25">
@@ -1563,150 +1563,150 @@
         <v>57</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.413820811570915</v>
+        <v>5.224187213962743</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>9.065792613243978</v>
+        <v>8.713241697072995</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.916635263576651</v>
+        <v>6.536105738499202</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.233841347220952</v>
+        <v>-5.513774699978562</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.526516865228928</v>
+        <v>-9.509015519024409</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-7.229142835593841</v>
+        <v>-5.738924645315045</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.559467229947728</v>
+        <v>-4.111732319519511</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.9910079859146634</v>
+        <v>2.408359306674626</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8243601355204433</v>
+        <v>0.6140476968891235</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.67427893185026</v>
+        <v>-0.9102482793337501</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.38417780462634</v>
+        <v>3.500717112553502</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.418555956981663</v>
+        <v>3.542252578009908</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.998405103668254</v>
+        <v>3.147094651446082</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.732912683719405</v>
+        <v>6.904911443286068</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 1.547</t>
+          <t>X ≈ 1.546</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>43</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.33303745783774</v>
+        <v>3.295403708175058</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.373014155471516</v>
+        <v>6.36682816947679</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.62940556141422</v>
+        <v>10.61278082029096</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.78288651895614</v>
+        <v>3.792448219892826</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.9190155705115401</v>
+        <v>0.9901879252354036</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.216389600146627</v>
+        <v>1.26048829283296</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.457260636229364</v>
+        <v>3.524026537809377</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6646105970937199</v>
+        <v>0.7377271700563455</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.721952954777834</v>
+        <v>-1.613499168396764</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.730453830287594</v>
+        <v>6.839568377824577</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.851334067376243</v>
+        <v>8.95340938643686</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.560130824382725</v>
+        <v>6.683827445410969</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.139979971069316</v>
+        <v>6.288669518847144</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.365715621295848</v>
+        <v>6.537714380862511</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 1.599</t>
+          <t>X ≈ 1.598</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>41</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.177620554831506</v>
+        <v>-0.1499152191186539</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.444483242255473</v>
+        <v>3.005848621256469</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8283369229873614</v>
+        <v>-2.293759718537416</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6981117793990776</v>
+        <v>-2.191697248314163</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.675425722738602</v>
+        <v>-5.157066207498481</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-8.256100473591317</v>
+        <v>-9.74378175517311</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.415286728118126</v>
+        <v>-0.0947095684085042</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.826266864819253</v>
+        <v>6.775078555934037</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.326260318052441</v>
+        <v>4.27125998556204</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.476341521722723</v>
+        <v>3.410335976758567</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.710664753706425</v>
+        <v>5.645219919466385</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1330058744260469</v>
+        <v>-0.009309253397802308</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.885867662504367</v>
+        <v>2.034557210282195</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.766445467756895</v>
+        <v>-2.594446708190233</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.48204693242856</v>
+        <v>10.45285113807593</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.240250271746334</v>
+        <v>-2.241437058190989</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.635021656501372</v>
+        <v>-2.635175046505694</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>15.47543245250976</v>
+        <v>15.52397837227553</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11.98439241917492</v>
+        <v>12.03240409816524</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.109916367980837</v>
+        <v>4.159163930374554</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.752637915161813</v>
+        <v>7.825895024941509</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.698017960571761</v>
+        <v>6.797925996590436</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.028692409223332</v>
+        <v>3.152389030251577</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.01594896331743</v>
+        <v>10.16463851109526</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>13.94538831724761</v>
+        <v>14.11738707681427</v>
       </c>
     </row>
     <row r="29">
@@ -1771,150 +1771,150 @@
         <v>31</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.093819256340758</v>
+        <v>-4.12301505069339</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.70500534940463</v>
+        <v>-5.706192135849285</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.873970282546772</v>
+        <v>-2.874123672551093</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.707867764267405</v>
+        <v>3.707373271889402</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.169578211171753</v>
+        <v>3.218124130937525</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.692758692419694</v>
+        <v>6.716716101369308</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.382241881540629</v>
+        <v>3.43025356053095</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.140979689366745</v>
+        <v>6.190227251760462</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>12.53161043606981</v>
+        <v>12.60486754584951</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.45588518812697</v>
+        <v>8.555232513421544</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.251184029866778</v>
+        <v>8.351092065885453</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.05975573060924</v>
+        <v>5.183452351637484</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.037814477542838</v>
+        <v>-4.889124929765011</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.812078827316306</v>
+        <v>-4.640080067749643</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 1.754</t>
+          <t>X ≈ 1.753</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-12.48091603053435</v>
+        <v>-9.65296896774413</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>10.19242537567145</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11.7717287488062</v>
+        <v>9.439322287619511</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.264230554892222</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-15.21032504780115</v>
+        <v>-19.42278222373574</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-9.393577177464344</v>
+        <v>-13.10375366169358</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-9.598278335724537</v>
+        <v>-13.30789410922967</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.897233516702443</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-16.65071770334938</v>
+        <v>-20.78774244128584</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.091648719789418</v>
+        <v>-6.252983293555992</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 1.806</t>
+          <t>X ≈ 1.805</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.332767882386257</v>
+        <v>-6.081540396315603</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.167157135661071</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-10.04242906390878</v>
+        <v>-8.058455469786111</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.606314598198104</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.068025045102303</v>
+        <v>9.439322287619454</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.365399074737553</v>
+        <v>6.140679235009856</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.576985011767619</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>12.75704752825821</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>15.16004532256922</v>
+        <v>16.29150349054998</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.31012652623936</v>
+        <v>15.467674909735</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>21.51283277538658</v>
+        <v>22.40639160505604</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>21.54721092774185</v>
+        <v>22.46455834242094</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>21.1270600744285</v>
+        <v>22.06940041585711</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>17.64909202095127</v>
+        <v>18.74701670644381</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>9</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.074639525021361</v>
+        <v>3.04544373066873</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-9.647657679153738</v>
+        <v>-9.648844465598394</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.068682047202181</v>
+        <v>1.068528657197859</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-21.02331503143153</v>
+        <v>-21.02380952380953</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6606176376953172</v>
+        <v>0.7091635574610891</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.51732377538813</v>
+        <v>11.56657133778184</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.45634161886568</v>
+        <v>11.52959872864538</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>21.71753393364678</v>
+        <v>21.81688125894135</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.6750112944803206</v>
+        <v>-0.551314673452076</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>21.1270600744285</v>
+        <v>21.27574962220633</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.8694264975670407</v>
+        <v>-0.6974277380003784</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>15</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>25.51312649164688</v>
+        <v>25.51297310164256</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>18.97668496856853</v>
+        <v>18.97619047619052</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>25.10506208213935</v>
+        <v>25.15360800190512</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>25.40243611177463</v>
+        <v>25.42639352072425</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25.31772575250837</v>
+        <v>25.36573743149869</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>24.85065710872173</v>
+        <v>24.89990467111544</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>31.45634161886547</v>
+        <v>31.52959872864516</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>23.93975615586909</v>
+        <v>24.03910348116366</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>23.73505499760884</v>
+        <v>23.83496303362752</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>23.34928229665076</v>
+        <v>23.49797184442858</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>13</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>9.057545507927188</v>
+        <v>9.028349713574556</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>30.52328249178643</v>
+        <v>30.52209570534178</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>22.43620341472371</v>
+        <v>22.43605002471939</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>14.87412086600431</v>
+        <v>14.87362637362631</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>22.02813900521638</v>
+        <v>22.07668492498215</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22.32551303485135</v>
+        <v>22.34947044380097</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>22.24080267558534</v>
+        <v>22.28881435457566</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.389118647183167</v>
+        <v>6.438366209576884</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.02044418296802</v>
+        <v>14.09370129274772</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.17052538663816</v>
+        <v>13.26987271193273</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.418791156237411</v>
+        <v>-2.318883120218736</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.307894688425662</v>
+        <v>5.431591309453907</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.58005152741988</v>
+        <v>12.72874107519771</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.49809486995418</v>
+        <v>20.67009362952084</v>
       </c>
     </row>
   </sheetData>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.4848</t>
+          <t>X &gt; 0.4849</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4083</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0267035763218928</v>
+        <v>-0.02594231684997084</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1580200063480817</v>
+        <v>0.1576246100546044</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02082255810170608</v>
+        <v>0.02077037259761738</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01774068704354193</v>
+        <v>0.01770481529194257</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1038398870771218</v>
+        <v>0.1024134626560667</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.04791288439067642</v>
+        <v>0.04721770994628827</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1233016879449025</v>
+        <v>0.1218349924742981</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1588762868038245</v>
+        <v>0.1572845198589405</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.06249119883452181</v>
+        <v>0.06058945582920927</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.08268322390618721</v>
+        <v>0.08010909502736752</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.03483484327247055</v>
+        <v>-0.03710727887252574</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.02493649507871964</v>
+        <v>-0.01407413621154063</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.05839101359487842</v>
+        <v>0.06856295336845619</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.02860599488116833</v>
+        <v>0.03824563388099733</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4001</v>
+        <v>4011</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1729588760193437</v>
+        <v>0.1737847953913416</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2199616849760915</v>
+        <v>0.2194130536658392</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1129769030155146</v>
+        <v>0.1126747426171022</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2817556252600824</v>
+        <v>0.2810068568586317</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3058602861803621</v>
+        <v>0.3028617332485055</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2427554730519788</v>
+        <v>0.2410240258249203</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2965128750439305</v>
+        <v>0.2935622199506511</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2924943528554209</v>
+        <v>0.2894988956610263</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2453553516994802</v>
+        <v>0.2414181177554369</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1085873247001601</v>
+        <v>0.1038606418111385</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.08208214953084081</v>
+        <v>-0.08631250199783835</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1226477893314097</v>
+        <v>-0.1138475527056144</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.07900356042075884</v>
+        <v>-0.07132027920057027</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.03590272568254704</v>
+        <v>0.0422049388049146</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3903</v>
+        <v>3912</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.2273108473399432</v>
+        <v>0.2301379839327993</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1373893151955841</v>
+        <v>0.1392455111708273</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.01345837542888972</v>
+        <v>-0.01112789300176331</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2841084749180922</v>
+        <v>0.2602040816326507</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2457270437762773</v>
+        <v>0.2186756211958496</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1223133182212024</v>
+        <v>0.09714390357253677</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.179547656295469</v>
+        <v>0.1525640845494891</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1360423147620651</v>
+        <v>0.1207369407094205</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.06361248420090249</v>
+        <v>0.05823458942301585</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1063385944511026</v>
+        <v>-0.1130926373246837</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3622561419558679</v>
+        <v>-0.3540535691822342</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.3022697949782582</v>
+        <v>-0.2816275105610302</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2214144246607646</v>
+        <v>-0.2025137165221338</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.08370611153934959</v>
+        <v>-0.06688922402643271</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3751</v>
+        <v>3758</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.4712116290401127</v>
+        <v>0.4622873258561171</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2308561099745816</v>
+        <v>0.2326134254136392</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1432488971816426</v>
+        <v>0.1453065234635389</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5395730295938463</v>
+        <v>0.5286776420605364</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3472121619691464</v>
+        <v>0.3461710829145161</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2068012967625563</v>
+        <v>0.2085401732214933</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2698024298246651</v>
+        <v>0.2687403546982594</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2434666959386647</v>
+        <v>0.2546748013306015</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01586580432752527</v>
+        <v>0.005105859480536878</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1050080327800842</v>
+        <v>-0.08636169693318863</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3629998918130042</v>
+        <v>-0.3288231934397956</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1953949875258871</v>
+        <v>-0.1494234204969942</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.04090960100386809</v>
+        <v>0.002361309711865545</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.03996062882872309</v>
+        <v>0.08017264045135875</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3589</v>
+        <v>3596</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1594397226618725</v>
+        <v>0.1521177924175063</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.03633824337429559</v>
+        <v>0.03871330848183874</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.009676622924963851</v>
+        <v>-0.007137855361698087</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5654873415755191</v>
+        <v>0.554066909782776</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.4721366093919528</v>
+        <v>0.4686232669621191</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3398491854880277</v>
+        <v>0.3403302225564602</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2982488465539959</v>
+        <v>0.2949237686272639</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.3474564407561331</v>
+        <v>0.3567222217957138</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1070468898380526</v>
+        <v>0.1253591655608801</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.08697734454872119</v>
+        <v>-0.07200762994754939</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.180288917735119</v>
+        <v>-0.1494770886287142</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.06236857657444261</v>
+        <v>-0.0201553874289786</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.02119124095374758</v>
+        <v>0.0172935013648825</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1088713879471825</v>
+        <v>0.1708209333627053</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3396</v>
+        <v>3401</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2960454740204597</v>
+        <v>0.2896536397861382</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.03566473382745272</v>
+        <v>-0.03289606337030193</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1499137906231383</v>
+        <v>-0.1468509452783593</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3919549871904451</v>
+        <v>0.3803168084482209</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2359059515896078</v>
+        <v>0.2298990817174342</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0200831705980633</v>
+        <v>0.0198775242463114</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.09854364012237227</v>
+        <v>0.09268986837478366</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2067489274385181</v>
+        <v>0.2140561684729434</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.001378608719342367</v>
+        <v>0.03028379421576943</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1874148773956534</v>
+        <v>-0.1606028330801905</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3038028181109595</v>
+        <v>-0.260219105032931</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2105491873923739</v>
+        <v>-0.1562384335330549</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.0713829962547905</v>
+        <v>-0.005849437170525107</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.005665209777639291</v>
+        <v>0.08338836183937559</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3160</v>
+        <v>3163</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5680571132255139</v>
+        <v>0.5626899400042902</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1430432619896891</v>
+        <v>0.1456017297302452</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2029658257733971</v>
+        <v>-0.1995111354319405</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2750304211978332</v>
+        <v>0.2628508356985151</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.2109741908969553</v>
+        <v>0.2009266138926051</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.03411489773722565</v>
+        <v>0.04930295587719513</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1248098764805405</v>
+        <v>0.1321515729128322</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.04020021491013637</v>
+        <v>-0.01802462181395015</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1960890465357252</v>
+        <v>-0.1496942006477155</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.4273324517259454</v>
+        <v>-0.387798950159457</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4421601922646232</v>
+        <v>-0.3848727212682874</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2179086221877782</v>
+        <v>-0.1511040362746172</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.0684392223366288</v>
+        <v>0.008717735705410234</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1275136986923755</v>
+        <v>-0.00891121009102136</v>
       </c>
     </row>
     <row r="13">
@@ -2578,153 +2578,153 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2900</v>
+        <v>2903</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3934385305671881</v>
+        <v>0.3906777391363576</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.06317650376347217</v>
+        <v>-0.05964661687427508</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4393364776952779</v>
+        <v>-0.4348290961597456</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5176196338572581</v>
+        <v>0.5037296952446368</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.496036935739177</v>
+        <v>0.480068483004878</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.06776712625509163</v>
+        <v>-0.05315271509572028</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1419848841417206</v>
+        <v>0.1456549005495873</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.03041838248830686</v>
+        <v>-0.01068680068658523</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2637548995763979</v>
+        <v>-0.2195988871273684</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2326576372344604</v>
+        <v>-0.1989426144676685</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1959794851498273</v>
+        <v>-0.1430135665101702</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.04529521892964539</v>
+        <v>0.1065549000801482</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.0734202276851903</v>
+        <v>0.1439773540704152</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.09225932618759458</v>
+        <v>0.2058523936640313</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.8992</t>
+          <t>X &gt; 0.8991</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2385866889683683</v>
+        <v>0.2213875939429215</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2413607601950574</v>
+        <v>0.2267420856952498</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2953970981786611</v>
+        <v>0.2979401686707348</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.319867964939647</v>
+        <v>1.301771871539316</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.248141397847071</v>
+        <v>1.221851507139803</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7679104508103052</v>
+        <v>0.7793803322059105</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.782525441345399</v>
+        <v>0.7790086771331417</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7822012549682213</v>
+        <v>0.8176384701064237</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6823237269946461</v>
+        <v>0.7418610491729538</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.115952188541101</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.9112510302809085</v>
+        <v>1.000011577316798</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.02341992553783</v>
+        <v>1.119236997099591</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.875536672380008</v>
+        <v>0.9795109038921979</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.984586208254143</v>
+        <v>1.134263984826489</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.951</t>
+          <t>X &gt; 0.9509</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2260</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3484385229581264</v>
+        <v>0.3325501407366431</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1316926574721435</v>
+        <v>0.1156136902215934</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4688787040361646</v>
+        <v>0.4711044370324942</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.13007729895196</v>
+        <v>1.110229276895943</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7687788962987412</v>
+        <v>0.7336697575293982</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6236750498276322</v>
+        <v>0.6338074660021746</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1849823896765059</v>
+        <v>0.2001745175913996</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.514373922880921</v>
+        <v>0.5731938543383066</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4533917663581448</v>
+        <v>0.53622124520151</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.019402173568103</v>
+        <v>1.106241290350837</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8589488029185333</v>
+        <v>0.9715074437025919</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.8933269552738565</v>
+        <v>1.010724819621899</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6944150400135527</v>
+        <v>0.8177418576970084</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7431595397975954</v>
+        <v>0.9151582993642577</v>
       </c>
     </row>
     <row r="16">
@@ -2737,98 +2737,98 @@
         <v>1894</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8946113956259865</v>
+        <v>0.8792733564057116</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2086894331300542</v>
+        <v>0.1894225981021975</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2121761220586009</v>
+        <v>0.2160734694827084</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9231826806416876</v>
+        <v>0.9004806970106642</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.6488846798163195</v>
+        <v>0.5981108951193193</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5766705362729496</v>
+        <v>0.58428825756625</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3863635560986438</v>
+        <v>0.3947000433996877</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.764067879576956</v>
+        <v>0.8240752872290855</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5446907916919912</v>
+        <v>0.6291247949959171</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.278721308984089</v>
+        <v>1.362601900552391</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.074020150723896</v>
+        <v>1.188679427934275</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.530784786711749</v>
+        <v>1.646294327954386</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.163432243852398</v>
+        <v>1.281613005378411</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9667814104464156</v>
+        <v>1.138780170013078</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 1.055</t>
+          <t>X &gt; 1.054</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1575</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9454799085519383</v>
+        <v>0.9327182446013254</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.019008987512933</v>
+        <v>0.9919922017701737</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.195666174186456</v>
+        <v>1.229966152811123</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.770335762219268</v>
+        <v>1.774336283185839</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.295538272615637</v>
+        <v>1.257339817211985</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7040234133618313</v>
+        <v>0.7428492169266718</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.127249562032176</v>
+        <v>1.160544271270695</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.422085680150197</v>
+        <v>1.518017400691022</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9801511426750409</v>
+        <v>1.101057457798682</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.35245456856741</v>
+        <v>2.467493848717424</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.084261346815147</v>
+        <v>2.236992202936285</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.372607753138723</v>
+        <v>2.522571395357851</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.888964836333251</v>
+        <v>2.037654384111079</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.797240169099467</v>
+        <v>1.96923892866613</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8060135905019976</v>
+        <v>0.8283379065021208</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.022448959993156</v>
+        <v>2.084761742297914</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.550278194433162</v>
+        <v>1.69102375398321</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.835302099631434</v>
+        <v>1.94086021505376</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.838808212170406</v>
+        <v>1.879203697523977</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8203927681212804</v>
+        <v>0.9648550591856804</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.200078693684837</v>
+        <v>1.254882928034483</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.352205096337727</v>
+        <v>1.48189081430241</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2850309893505525</v>
+        <v>0.4441483822248884</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.292697332339579</v>
+        <v>1.5121389203007</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.707191220519022</v>
+        <v>1.969118777652149</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.896368134484248</v>
+        <v>2.149302610498538</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.708415423585691</v>
+        <v>1.87635022280692</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.701952931397372</v>
+        <v>1.970954930382128</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.921308251207996</v>
+        <v>1.909777677875446</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.143519397737627</v>
+        <v>3.089031531946119</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.841512391461251</v>
+        <v>2.787374574938958</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.064501913528275</v>
+        <v>2.970046082949303</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.340683603475256</v>
+        <v>2.164678112606332</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.081471362238361</v>
+        <v>2.028424914999313</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.429449342856024</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.550100522450748</v>
+        <v>2.60996930638774</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.118060852013322</v>
+        <v>2.203652283585193</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.937900868299415</v>
+        <v>3.003983333289263</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.382550359389874</v>
+        <v>3.501938056754206</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.231399754787866</v>
+        <v>3.33757421543681</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.811248901474457</v>
+        <v>2.904830046467467</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.758691416265002</v>
+        <v>2.875839690688572</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.321581131781201</v>
+        <v>1.266663823365555</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.115616378104427</v>
+        <v>3.065673885898534</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.061367127288094</v>
+        <v>3.122894183942343</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.829503735121627</v>
+        <v>1.850532086423726</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.858751071923784</v>
+        <v>1.763777493430638</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.361573455701894</v>
+        <v>1.471591260837144</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.86596638814968</v>
+        <v>2.992856075566486</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.852927256281212</v>
+        <v>3.091995066595565</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.564930343799304</v>
+        <v>2.8290337568938</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.736577949285568</v>
+        <v>2.975755064873972</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.326428436882352</v>
+        <v>3.517862240875495</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.02028445529897</v>
+        <v>3.190181925187375</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.486626224005995</v>
+        <v>2.681645313816297</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.825869252212094</v>
+        <v>2.930690175831664</v>
       </c>
     </row>
     <row r="21">
@@ -2994,101 +2994,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.652698596751158</v>
+        <v>2.72001369812557</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.151217145037549</v>
+        <v>3.228886822174736</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.319033664642568</v>
+        <v>3.393028889648036</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.761495095150757</v>
+        <v>1.788108539505181</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.78579344641512</v>
+        <v>1.657104505401726</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.66122654778016</v>
+        <v>1.790029884360507</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.561045021144096</v>
+        <v>2.708394774156034</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.375270329537386</v>
+        <v>2.662142433353111</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.454935149104614</v>
+        <v>2.765029964076454</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.308251233224837</v>
+        <v>2.582520848110349</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.947431931504717</v>
+        <v>3.161751252421297</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.997281251229943</v>
+        <v>2.179646624924949</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.43648342182653</v>
+        <v>1.644039260158884</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.943513024233091</v>
+        <v>2.173982998578737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 1.314</t>
+          <t>X &gt; 1.313</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>601</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.758684635023045</v>
+        <v>3.760515237819284</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.977781403856063</v>
+        <v>3.992519670815255</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.915788721264086</v>
+        <v>3.928814685800873</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.382120354037141</v>
+        <v>2.337072018890197</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.511052098778386</v>
+        <v>1.279435816474759</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.30925807516887</v>
+        <v>1.386658421386393</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.722051875636488</v>
+        <v>2.816068557326503</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.754151285094345</v>
+        <v>3.012487452572302</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.526779777490034</v>
+        <v>2.809951929528211</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.841586438730893</v>
+        <v>3.077246101395737</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.801610738041411</v>
+        <v>3.967853399075985</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.839316677418367</v>
+        <v>1.963013298446612</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.751944526268019</v>
+        <v>1.900634074045847</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.144069527576086</v>
+        <v>2.316068287142748</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>500</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.919083969465653</v>
+        <v>2.847031032255877</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.707897876401816</v>
+        <v>3.644806328052397</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.513126491646773</v>
+        <v>3.449481038150402</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.043351635235133</v>
+        <v>1.905282590173236</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.10506208213944</v>
+        <v>1.813647763336633</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>1.490011810982601</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.517725752508362</v>
+        <v>3.616234449391328</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.85065710872162</v>
+        <v>3.150401689007985</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.789674952198844</v>
+        <v>3.113429079871189</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.33975615586899</v>
+        <v>3.600856469211379</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.735054997608799</v>
+        <v>4.912807345004722</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.769433149964122</v>
+        <v>2.893129770992367</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.749282296650712</v>
+        <v>2.89797184442854</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.975017946877244</v>
+        <v>3.147016706443907</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>428</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.191981165727327</v>
+        <v>2.01425012406893</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.319112829672846</v>
+        <v>4.143370022671775</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.559855463609395</v>
+        <v>5.373761964751509</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.820921728693087</v>
+        <v>3.647497514086837</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.983566755036641</v>
+        <v>3.622285496104759</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.64542676598014</v>
+        <v>2.73497820749909</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.663520145031733</v>
+        <v>4.762489171637895</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.495516921805745</v>
+        <v>3.832619288284711</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.135469344722217</v>
+        <v>4.491702363602684</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.154709426897028</v>
+        <v>5.43445231837287</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.585522287328423</v>
+        <v>6.772025970690414</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.28345184155291</v>
+        <v>4.407148462581155</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.330590707865667</v>
+        <v>4.479280255643495</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.32268149827911</v>
+        <v>4.494680257845772</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>362</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.938973472228078</v>
+        <v>1.73646351757877</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.852649257617287</v>
+        <v>5.632738487217438</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.562850248552863</v>
+        <v>6.334890909861642</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.759373734682661</v>
+        <v>4.546966731898237</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.773570369432271</v>
+        <v>4.331690193686043</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.518458211222054</v>
+        <v>4.604475712504971</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.367449509414449</v>
+        <v>6.461627842457595</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.90038086562771</v>
+        <v>6.269767684813978</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.115641803027579</v>
+        <v>6.506767678416907</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.475667758078941</v>
+        <v>7.775367217427295</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.375938975509357</v>
+        <v>8.573255044646757</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.647886188638154</v>
+        <v>5.771582809666398</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.056464617092701</v>
+        <v>6.205154164870528</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.177227891628633</v>
+        <v>5.349226651195295</v>
       </c>
     </row>
     <row r="26">
@@ -3257,98 +3257,98 @@
         <v>305</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.289575772744335</v>
+        <v>1.084659416943083</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.25216017148378</v>
+        <v>5.057037887342787</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.496733049023824</v>
+        <v>6.297286827132652</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.626958192612186</v>
+        <v>6.427170868347332</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>7.072275196893543</v>
+        <v>6.918313884258161</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.713911521610605</v>
+        <v>6.537504631835262</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.596414277098532</v>
+        <v>8.437632856335284</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.817870223475722</v>
+        <v>6.9914079390892</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.412625771870978</v>
+        <v>7.608030101194231</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.18565779521326</v>
+        <v>9.398580605346567</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.308825489412072</v>
+        <v>9.521237543431397</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.064515117177237</v>
+        <v>6.188211738205482</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.627970821240879</v>
+        <v>6.776660369018707</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.886493356713316</v>
+        <v>5.058492116279979</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 1.573</t>
+          <t>X &gt; 1.572</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>262</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.9541984732824389</v>
+        <v>0.7218273386111136</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.068203219913272</v>
+        <v>4.842072306687207</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.818470003097161</v>
+        <v>5.589018729018889</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.093733314624451</v>
+        <v>6.859587180879956</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.08216131878067</v>
+        <v>7.891250587456554</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.616176569789801</v>
+        <v>7.40357983251122</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.43986315708851</v>
+        <v>9.244064427696408</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.82775634536285</v>
+        <v>8.017775393548803</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.911812356778995</v>
+        <v>9.1214871950584</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.588611117701049</v>
+        <v>9.818571161771928</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.383909959440857</v>
+        <v>9.614430714235837</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.983173607979388</v>
+        <v>6.106870229007633</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.708060922604908</v>
+        <v>6.856750470382735</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.643720236953584</v>
+        <v>4.815718996520246</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>221</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.9127491278366904</v>
+        <v>0.8835533334840591</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.183915975949333</v>
+        <v>5.182729189504677</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.05158803010832</v>
+        <v>7.051434640103999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.539279237045093</v>
+        <v>8.53878474466709</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>10.26343312286343</v>
+        <v>10.3119790426292</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>10.56080715249851</v>
+        <v>10.58476456144813</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.92858548101515</v>
+        <v>10.97659716000547</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.199073398314383</v>
+        <v>8.248320960708099</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.948045992922829</v>
+        <v>10.02130310270253</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>10.90808194772418</v>
+        <v>11.00742927301876</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.25089210168119</v>
+        <v>10.35080013769986</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.117849439556878</v>
+        <v>7.241546060585122</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.602675961809084</v>
+        <v>7.751365509586911</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.018456860904394</v>
+        <v>6.190455620471056</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>194</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4190603604312528</v>
+        <v>-0.4482561547838841</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.217176226917282</v>
+        <v>6.215989440472626</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.399724429791107</v>
+        <v>8.399571039786785</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.014485655853697</v>
+        <v>8.013991163475694</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>9.538051772861103</v>
+        <v>9.586597692626874</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>10.35088972002195</v>
+        <v>10.37484712897157</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10.78164327828156</v>
+        <v>10.82965495727188</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.768182881917497</v>
+        <v>8.817430444311213</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.25359247797205</v>
+        <v>10.32684958775175</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.9500654342195</v>
+        <v>11.04941275951407</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.7453642759593</v>
+        <v>10.84527231197798</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7.686958923159992</v>
+        <v>7.810655544188236</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.266808069846583</v>
+        <v>7.415497617624411</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.915224132444258</v>
+        <v>5.087222892010921</v>
       </c>
     </row>
     <row r="30">
@@ -3465,150 +3465,150 @@
         <v>163</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2798201657846633</v>
+        <v>0.250624371432032</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.484584992966241</v>
+        <v>8.483398206521585</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.54380133827255</v>
+        <v>10.54364794826823</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.833535684314896</v>
+        <v>8.833041191936893</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10.74923386128055</v>
+        <v>10.79777978104632</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.04660789091564</v>
+        <v>11.07056529986525</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12.18889139668015</v>
+        <v>12.23690307567047</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.267835022832053</v>
+        <v>9.317082585225769</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.820349798824623</v>
+        <v>9.893606908604319</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.42441873255611</v>
+        <v>11.52376605785068</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.21971757429591</v>
+        <v>11.31962561031459</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.186611064074548</v>
+        <v>8.310307685102792</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>9.606951008307149</v>
+        <v>9.755640556084977</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.765201995957</v>
+        <v>6.937200755523662</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 1.78</t>
+          <t>X &gt; 1.779</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.573138023519704</v>
+        <v>1.181163342898252</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.745735714239657</v>
+        <v>8.3228184725075</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.37799135651165</v>
+        <v>10.61364424258205</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.48118947307298</v>
+        <v>8.73010546500479</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.64560262267998</v>
+        <v>10.92542008244214</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.29432800366644</v>
+        <v>11.86934654085837</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12.88529332007593</v>
+        <v>12.47983139123023</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.715521973586497</v>
+        <v>10.00057581205494</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12.35724251976642</v>
+        <v>12.6481669613074</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>13.53435075046359</v>
+        <v>13.83776119928437</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.3296495922034</v>
+        <v>13.63362075174828</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.309973690504656</v>
+        <v>9.664941851529285</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.26820121556963</v>
+        <v>12.62548862295203</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.764207136066439</v>
+        <v>8.176546907786182</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 1.832</t>
+          <t>X &gt; 1.831</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>121</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.890984795911933</v>
+        <v>2.861789001559302</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.544261512765452</v>
+        <v>9.543074726320796</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>14.93461409495257</v>
+        <v>14.93446070494825</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.453268990607043</v>
+        <v>8.45277449822904</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.2207645614783</v>
+        <v>11.26931048124407</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>13.17103115309685</v>
+        <v>13.19498856204646</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>14.73921335581416</v>
+        <v>14.78722503480448</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.313467026076999</v>
+        <v>9.362714588470716</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.73182371252943</v>
+        <v>11.80508082230913</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.36124375917478</v>
+        <v>13.46059108446936</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.50365003893111</v>
+        <v>11.60355807494979</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.579350505336024</v>
+        <v>6.703047126364268</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.2914310569813</v>
+        <v>10.44012060475912</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.558489021257415</v>
+        <v>5.730487780824078</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>112</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.876226826608509</v>
+        <v>2.847031032255877</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>11.08646930497325</v>
+        <v>11.08528251852859</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16.04884077736107</v>
+        <v>16.04868738735675</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.82192306380657</v>
+        <v>10.82142857142857</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>12.06934779642516</v>
+        <v>12.11789371619093</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>14.15243611177453</v>
+        <v>14.17639352072415</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14.9605828953655</v>
+        <v>15.00859457435583</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.136371394435919</v>
+        <v>9.185618956829636</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.75396066648456</v>
+        <v>11.82721777626426</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.68975615586899</v>
+        <v>12.78910348116356</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.59219785475166</v>
+        <v>11.69210589077034</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.162290292821261</v>
+        <v>7.285986913849506</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.420710868079283</v>
+        <v>9.56940041585711</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.075017946877246</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>97</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.158259227197604</v>
+        <v>2.129063432844973</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.85635148464924</v>
+        <v>10.85516469820458</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>14.58529144010038</v>
+        <v>14.58513805009606</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.560877408431011</v>
+        <v>9.560382916053008</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.05351569038687</v>
+        <v>10.10206161015264</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.41274539012504</v>
+        <v>12.43670279907465</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.35896286591043</v>
+        <v>13.40697454490075</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.706327211814411</v>
+        <v>6.755574774208128</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.707200725394721</v>
+        <v>8.780457835174417</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.9500654342195</v>
+        <v>11.04941275951407</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.714436440907761</v>
+        <v>9.814344476926436</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.656031088108449</v>
+        <v>6.779727709136694</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.266808069846583</v>
+        <v>7.415497617624411</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.43068804997003</v>
+        <v>5.602686809536692</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>13.37026934878964</v>
+        <v>13.37011595878532</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.738589730473237</v>
+        <v>8.738095238095234</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.200300177377542</v>
+        <v>8.248846097143314</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>10.87862658796502</v>
+        <v>10.90258399691463</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.755419013483532</v>
+        <v>6.804666575877249</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.59219785475166</v>
+        <v>11.69210589077034</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>6.864671245202217</v>
+        <v>6.988367866230462</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>6.444520391888808</v>
+        <v>6.593209939666636</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>3.098827470686771</v>
+        <v>3.270826230253434</v>
       </c>
     </row>
   </sheetData>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.4848</t>
+          <t>X &lt; 0.4849</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1330331559557862</v>
+        <v>-0.08448723619001441</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.270106704889322</v>
+        <v>1.318118383879643</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.463565679678517</v>
+        <v>3.56291300497309</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.211245473799281</v>
+        <v>9.311153509817956</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.829674113819543</v>
+        <v>8.178844056706659</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.795065429180831</v>
+        <v>4.212257558714249</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.020801079407363</v>
+        <v>4.461302420729616</v>
       </c>
     </row>
     <row r="7">
@@ -3960,49 +3960,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.685735307642787</v>
+        <v>-3.714931101995418</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.284873207935533</v>
+        <v>-2.286059994380189</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.8724156770279166</v>
+        <v>-0.8725690670322379</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.790334972562817</v>
+        <v>-2.766377563613204</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.477454970383199</v>
+        <v>-3.429443291392879</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.944523614169938</v>
+        <v>-3.895276051776221</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.198276855030059</v>
+        <v>-2.125019745250363</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.168671818519599</v>
+        <v>1.268019143814172</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.783247768693144</v>
+        <v>5.883155804711819</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.799736180267146</v>
+        <v>6.543732180630926</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.773524720893143</v>
+        <v>5.546164615512886</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.362896734756035</v>
+        <v>2.18075164620295</v>
       </c>
     </row>
     <row r="8">
@@ -4012,49 +4012,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.04695376638341</v>
+        <v>-3.071909577695976</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1298379726547836</v>
+        <v>-0.1607046403799188</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.362183095420363</v>
+        <v>1.318216547335346</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.658535157217692</v>
+        <v>-2.297217763509899</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.064749238615271</v>
+        <v>-1.662871398843848</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1194172438500019</v>
+        <v>0.4825732960050502</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3426516059821978</v>
+        <v>0.04738537157359701</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.05500326863686666</v>
+        <v>0.1630625658521936</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.393448537104511</v>
+        <v>1.466705646884208</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>7.750206512760315</v>
+        <v>7.608547939287845</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.887303872397581</v>
+        <v>6.53463920495463</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.706696745319917</v>
+        <v>5.384764297258727</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.270835437371545</v>
+        <v>2.992299725311831</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.032228679699031</v>
+        <v>-3.931912772754281</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.8701450830253918</v>
+        <v>-0.8866380786889181</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.5489260143198109</v>
+        <v>-0.5677869933694168</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.878179465243328</v>
+        <v>-3.763318629114359</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.137144152872537</v>
+        <v>-2.114800549163668</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.64072935585137</v>
+        <v>-0.654366574287728</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9652478685947514</v>
+        <v>-0.9525523547245882</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.9527002054270568</v>
+        <v>-1.052476281265612</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.624207326299569</v>
+        <v>1.426177885367565</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.452945604310244</v>
+        <v>2.2729936959607</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.792747305301113</v>
+        <v>4.455488093293347</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.287505439120757</v>
+        <v>2.843010439250129</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.903499164120589</v>
+        <v>1.493198574738805</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.9244155372386942</v>
+        <v>0.5489260143198038</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8458041544586195</v>
+        <v>-0.7977830577637022</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.6411164650420957</v>
+        <v>0.6236922220326306</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.5905791594608871</v>
+        <v>0.573007406959789</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.804924226833826</v>
+        <v>-2.72764028424406</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.217908556893363</v>
+        <v>-2.187729905470427</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.229688240557074</v>
+        <v>-1.228838040167794</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7962638847973338</v>
+        <v>-0.7749143695304781</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.263332528584073</v>
+        <v>-1.320026600362318</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4028010316461774</v>
+        <v>0.2846188089664992</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.625421095419945</v>
+        <v>1.526194703194548</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.212563648127826</v>
+        <v>2.010522414006132</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.481738175960658</v>
+        <v>1.208103953436435</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.234897547950538</v>
+        <v>0.9850630664595244</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2474616210540219</v>
+        <v>-0.1428283882204653</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.192256236719921</v>
+        <v>-1.162229925015353</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.8048050928966717</v>
+        <v>0.7910298560240037</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.054363605048842</v>
+        <v>1.039965389560201</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.19535804218421</v>
+        <v>-1.143775247888357</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5021730599794125</v>
+        <v>-0.4762120495086606</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.5703947681052881</v>
+        <v>0.5677816955313375</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.356485442430845</v>
+        <v>0.3785909019357021</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2397821677641545</v>
+        <v>-0.273840502629831</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.8051988849284797</v>
+        <v>0.6619011341434984</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.637039467641308</v>
+        <v>1.513330285287275</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.154744116779781</v>
+        <v>1.953519734658407</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.746086846462184</v>
+        <v>1.496222554497514</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.141490088858511</v>
+        <v>0.8433326691708061</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.3191816548975126</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.691961395425871</v>
+        <v>-1.674320281130839</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.04990971072134442</v>
+        <v>0.04056935767370362</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9371896080175972</v>
+        <v>0.9263589284141105</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4573393815466957</v>
+        <v>-0.420134983127106</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2506691431569976</v>
+        <v>-0.220407746126277</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3974905133571198</v>
+        <v>0.3476533632438361</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2138681857427827</v>
+        <v>0.1885720771679829</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6370072570895857</v>
+        <v>0.5649293016572159</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.225318516555284</v>
+        <v>1.075949813457832</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.95955813606701</v>
+        <v>1.830030502859813</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.01057531475449</v>
+        <v>1.823128714100847</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.30911568964666</v>
+        <v>1.092340816357265</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.8467996750022522</v>
+        <v>0.5985635604048767</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.9308827580104548</v>
+        <v>0.5517504342545578</v>
       </c>
     </row>
     <row r="13">
@@ -4272,153 +4272,153 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8325643821826958</v>
+        <v>-0.8264783088337353</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5389810789135936</v>
+        <v>0.5305355413678257</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.24311079305965</v>
+        <v>1.2339762364387</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8609688675142664</v>
+        <v>-0.8304970891177774</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.8068876033951469</v>
+        <v>-0.7711568883769147</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5558586137414849</v>
+        <v>0.5204374078714835</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1564354299277184</v>
+        <v>0.1463016948215738</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4761488475099824</v>
+        <v>0.429316435821228</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.088887550624051</v>
+        <v>0.9853810415703776</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.02637032909734</v>
+        <v>0.9464818171133302</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.9454568888617558</v>
+        <v>0.820834305213026</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3940388281975657</v>
+        <v>0.2510575574915848</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3342862429806317</v>
+        <v>0.169871373470933</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2100890369246429</v>
+        <v>-0.05204137832846101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.8992</t>
+          <t>X &lt; 0.8991</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1595</v>
+        <v>1605</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3313833202539769</v>
+        <v>-0.3037724836812643</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.07341053481312798</v>
+        <v>-0.05100035282890047</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2812660317177134</v>
+        <v>-0.2866535318360732</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.862882778729947</v>
+        <v>-1.836918837229973</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.744594811185571</v>
+        <v>-1.70389044240094</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9146675086998783</v>
+        <v>-0.9332828949572445</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8745339228973776</v>
+        <v>-0.8694834770265132</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.9332279631084859</v>
+        <v>-0.9905062877887616</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7103250478011418</v>
+        <v>-0.8068498694856245</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.401081867895861</v>
+        <v>-1.5060678584003</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.070952511777939</v>
+        <v>-1.211765938335141</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.252482942709641</v>
+        <v>-1.402820384770877</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.011619958988391</v>
+        <v>-1.174925351833146</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.252568260019309</v>
+        <v>-1.486628153369175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.951</t>
+          <t>X &lt; 0.9509</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1906</v>
+        <v>1917</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.368239974196328</v>
+        <v>-0.3497786650743819</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1071675686292579</v>
+        <v>0.1254610899571702</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3919334979202489</v>
+        <v>-0.3963546732402889</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.120740222802439</v>
+        <v>-1.100238219310661</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6912825653801349</v>
+        <v>-0.6514988245669002</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4700821745368557</v>
+        <v>-0.4829342541586001</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1007890039459056</v>
+        <v>0.08173534707971442</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3376274101068191</v>
+        <v>-0.4077074248179144</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2129414789890092</v>
+        <v>-0.311820155027192</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.876997770832574</v>
+        <v>-0.9791542131504727</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.686107914910842</v>
+        <v>-0.8181407744059186</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.727422195947824</v>
+        <v>-0.8643037188354938</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4892074778642268</v>
+        <v>-0.6334835546324982</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.6012674676033427</v>
+        <v>-0.8017574197950026</v>
       </c>
     </row>
     <row r="16">
@@ -4428,101 +4428,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2272</v>
+        <v>2283</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7069344273806095</v>
+        <v>-0.6955075397973474</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.04718828376056194</v>
+        <v>0.0624416236404528</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.04096899674568277</v>
+        <v>-0.04501376925470169</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5880243507420673</v>
+        <v>-0.5715848702719626</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.35745435801838</v>
+        <v>-0.3168515166943422</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2554586250675754</v>
+        <v>-0.2628843786194039</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.05305090391988898</v>
+        <v>-0.06095841095208243</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4083420133152416</v>
+        <v>-0.4591145933329983</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.18177871490699</v>
+        <v>-0.2531432774870623</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.787836111266337</v>
+        <v>-0.8579617838386255</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6165933540395514</v>
+        <v>-0.711686112233231</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9974973689452895</v>
+        <v>-1.091539523795191</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.6894330575067826</v>
+        <v>-0.785865212076061</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.5711088136861306</v>
+        <v>-0.7120284096314293</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 1.055</t>
+          <t>X &lt; 1.054</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2591</v>
+        <v>2602</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5408468795547137</v>
+        <v>-0.5346611152590626</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.4232584816465916</v>
+        <v>-0.4094823098893414</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6052439925961082</v>
+        <v>-0.6290614473018721</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.915664127932871</v>
+        <v>-0.9214422813271241</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.625707148629786</v>
+        <v>-0.6045493877300956</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2304996327425854</v>
+        <v>-0.25498843704937</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.4482480735116496</v>
+        <v>-0.4691953899984327</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6633975697535419</v>
+        <v>-0.7222151445528624</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3567040924852733</v>
+        <v>-0.4309596014866912</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.185484691915207</v>
+        <v>-1.254788182301674</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.022076845105161</v>
+        <v>-1.113173731643364</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.197786286981504</v>
+        <v>-1.285510259741393</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.902260913225831</v>
+        <v>-0.9891583899164473</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8865798917950798</v>
+        <v>-0.987802663271701</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2874</v>
+        <v>2882</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3326138822322022</v>
+        <v>-0.3452347899025696</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.7310487625448232</v>
+        <v>-0.7668855836395139</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5873934390291282</v>
+        <v>-0.6568709191547626</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6811976019354589</v>
+        <v>-0.7349591483040427</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6805778762372441</v>
+        <v>-0.7042776133460862</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1909018479756313</v>
+        <v>-0.2581818692238613</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3261479024725418</v>
+        <v>-0.3535000035099785</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4271206690561442</v>
+        <v>-0.4884448434477662</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.08665306960072172</v>
+        <v>0.01381655729592524</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3618421763061264</v>
+        <v>-0.463151114743475</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5471834452135838</v>
+        <v>-0.6672915622795657</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6325139988536748</v>
+        <v>-0.7478691884249073</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.546369877262336</v>
+        <v>-0.6227357518253669</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.579470570868061</v>
+        <v>-0.7012830853673293</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3088</v>
+        <v>3098</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.6422063531149931</v>
+        <v>-0.6415551238560511</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.9308118010175335</v>
+        <v>-0.9189415043064457</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.8889386906700949</v>
+        <v>-0.8764530750177641</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.9350860665079139</v>
+        <v>-0.9077553652021777</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6811826708473134</v>
+        <v>-0.6233101154384286</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5600961879670621</v>
+        <v>-0.543948194298423</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6596571230974533</v>
+        <v>-0.6516763060053421</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.721417875118064</v>
+        <v>-0.7452566192072325</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5384854099091285</v>
+        <v>-0.571078909302507</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.820916547882625</v>
+        <v>-0.8463434371971985</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9753946950472994</v>
+        <v>-1.018215411032095</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9231234843400813</v>
+        <v>-0.9600486736672025</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7750297784544955</v>
+        <v>-0.8066425473107302</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7902670272160179</v>
+        <v>-0.8301298397148997</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3285</v>
+        <v>3295</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3280961396914108</v>
+        <v>-0.3151375590680345</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.6799092209594164</v>
+        <v>-0.6711205272445326</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.7247375860231173</v>
+        <v>-0.7457363803327013</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3657530688619701</v>
+        <v>-0.3735015363309913</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3715620830093158</v>
+        <v>-0.3477552213604582</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2094679270958011</v>
+        <v>-0.2402731459425169</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5814237007115537</v>
+        <v>-0.6178939719569101</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6066507004549138</v>
+        <v>-0.6731699195456642</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4990788471932461</v>
+        <v>-0.5723120993802624</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5418491953015803</v>
+        <v>-0.6075449871409546</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6992515717342656</v>
+        <v>-0.7510242275190251</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.6175458582500539</v>
+        <v>-0.6625268865751224</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4729940271472159</v>
+        <v>-0.5250864079986428</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5954538948274717</v>
+        <v>-0.6232412601721791</v>
       </c>
     </row>
     <row r="21">
@@ -4688,101 +4688,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3455</v>
+        <v>3465</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5201317168088551</v>
+        <v>-0.5377536331219375</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5011012582967709</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5918937045447876</v>
+        <v>-0.6120629110340019</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2440942522107434</v>
+        <v>-0.2516977404617862</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.247131913241617</v>
+        <v>-0.2223643403592632</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1938676710727094</v>
+        <v>-0.2220214648666285</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3495186149093144</v>
+        <v>-0.3823167627936144</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.338594552647919</v>
+        <v>-0.3999799886309034</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.325931984217334</v>
+        <v>-0.3923318549525163</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.2926809646860846</v>
+        <v>-0.3508590224418526</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.423418108232724</v>
+        <v>-0.4684693286453836</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2282527048232623</v>
+        <v>-0.2660856890595511</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1113658514974389</v>
+        <v>-0.1546536604762423</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.2455319807638503</v>
+        <v>-0.2933873339601263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 1.314</t>
+          <t>X &lt; 1.313</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3565</v>
+        <v>3576</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6083615308138377</v>
+        <v>-0.6127903963155532</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5276626491782821</v>
+        <v>-0.5348183546423328</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.5718846940355462</v>
+        <v>-0.5785958542480998</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2867182948347846</v>
+        <v>-0.2812076254287348</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1383626520519385</v>
+        <v>-0.1004400159618939</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.07755269315129709</v>
+        <v>-0.09161820784329677</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2869774949720352</v>
+        <v>-0.3046536299538189</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3187632217180294</v>
+        <v>-0.3641355635870838</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2523418545238343</v>
+        <v>-0.3019645282953505</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3023284616709319</v>
+        <v>-0.3432330196748978</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4633754956647422</v>
+        <v>-0.4914763179655992</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.133005874426118</v>
+        <v>-0.1538238343737603</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1167861273537767</v>
+        <v>-0.141949877684965</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2117983224074678</v>
+        <v>-0.2406790429968027</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3666</v>
+        <v>3677</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3743653374112199</v>
+        <v>-0.3668671151745642</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3672516613904619</v>
+        <v>-0.361945626460745</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3938629018805528</v>
+        <v>-0.3882212523206263</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.167312129726767</v>
+        <v>-0.1497595780983403</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1738494824863963</v>
+        <v>-0.1355584384966306</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.06518714195917852</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3125492270723527</v>
+        <v>-0.3283674313103262</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2473821069646434</v>
+        <v>-0.2903127201890001</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2116870744968722</v>
+        <v>-0.2580247197556176</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2836770866378231</v>
+        <v>-0.3207769211196592</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4731761280385172</v>
+        <v>-0.4977360693896529</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2054850615953114</v>
+        <v>-0.222118937895921</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.2013040136847124</v>
+        <v>-0.2214408798781449</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2602248245357401</v>
+        <v>-0.2834429073717004</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3738</v>
+        <v>3749</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2281834258955868</v>
+        <v>-0.2089679036313257</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3587687902648469</v>
+        <v>-0.3412931676266524</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5524910063526889</v>
+        <v>-0.5344051256665665</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.327832996568489</v>
+        <v>-0.3102844971854566</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3446310056641337</v>
+        <v>-0.3057794814503083</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1661704018399845</v>
+        <v>-0.1782948117212371</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3698576920844303</v>
+        <v>-0.3843291818772769</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2615223784578546</v>
+        <v>-0.3026539642791093</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3078404098102396</v>
+        <v>-0.3516773755047851</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4215479595772962</v>
+        <v>-0.4556979051334267</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5846456172000813</v>
+        <v>-0.6065192377668183</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3214759409449712</v>
+        <v>-0.3350760407911579</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.3254970561174062</v>
+        <v>-0.3420281555714624</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3522158679970246</v>
+        <v>-0.3714148753112241</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3804</v>
+        <v>3815</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1623412335733931</v>
+        <v>-0.1440987529915603</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4233390208728096</v>
+        <v>-0.4060504163189833</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5419193799128479</v>
+        <v>-0.5241705028566273</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.345111920087362</v>
+        <v>-0.327838827838832</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3447149962764939</v>
+        <v>-0.3056958452552081</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2953603205444608</v>
+        <v>-0.306590772469562</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4445413689820512</v>
+        <v>-0.457776577404168</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4249334424594693</v>
+        <v>-0.4641602843587265</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4190412462784465</v>
+        <v>-0.4606204661849347</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5455379617780665</v>
+        <v>-0.5770872445372461</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6305872403738633</v>
+        <v>-0.6502347656913585</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3713971180337765</v>
+        <v>-0.3824793461153035</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.4089305811416679</v>
+        <v>-0.4223635853408538</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3524268480754387</v>
+        <v>-0.3683175006334167</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3861</v>
+        <v>3872</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.08029651582087638</v>
+        <v>-0.06417979605073043</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2836848759865092</v>
+        <v>-0.2689263038105452</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4321214422375093</v>
+        <v>-0.4169599225718628</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4170978610190517</v>
+        <v>-0.401976662863035</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4504934734161097</v>
+        <v>-0.4391755032494231</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3975121952815499</v>
+        <v>-0.3843824524648198</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5199164398390934</v>
+        <v>-0.5084245076452021</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4040623120179561</v>
+        <v>-0.418640595843641</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4250172361094755</v>
+        <v>-0.4415055025209398</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.5621843357222147</v>
+        <v>-0.5802513575461177</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5713632218528986</v>
+        <v>-0.5894045451025178</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3154749525468787</v>
+        <v>-0.3247329032461508</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3586410591234994</v>
+        <v>-0.3698308924679239</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2478258759665835</v>
+        <v>-0.2612477563660107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 1.573</t>
+          <t>X &lt; 1.572</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3904</v>
+        <v>3915</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.04282565524714954</v>
+        <v>-0.02730051854626936</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2105903769178923</v>
+        <v>-0.1961926288405991</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3106282976252501</v>
+        <v>-0.2959440958097659</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3709559784592855</v>
+        <v>-0.3561234891510168</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4354439234828362</v>
+        <v>-0.4237562601391289</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3797724771825202</v>
+        <v>-0.3665692533706988</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4761888473382214</v>
+        <v>-0.4644079395801128</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3923096431965263</v>
+        <v>-0.4062177778642493</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4392838607968059</v>
+        <v>-0.4547510204404333</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.481942922943702</v>
+        <v>-0.4989261257787518</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.4676580814800175</v>
+        <v>-0.484669338085574</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2397834398976357</v>
+        <v>-0.2477944056734529</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2870813397129268</v>
+        <v>-0.2967166131812675</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1749820531227542</v>
+        <v>-0.1865720547310588</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3945</v>
+        <v>3956</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.03018333725491829</v>
+        <v>-0.02837839077259474</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1623573674697951</v>
+        <v>-0.1618372971396127</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3159938319123654</v>
+        <v>-0.3151085721664728</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.37434747980911</v>
+        <v>-0.3732800230531055</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4690400928731933</v>
+        <v>-0.4706038518148361</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4614647230344673</v>
+        <v>-0.4615984066219667</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4565657454673371</v>
+        <v>-0.4581333734470547</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.3277787303064699</v>
+        <v>-0.3297773076832442</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4001984655226636</v>
+        <v>-0.4034148201219381</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4512289036397448</v>
+        <v>-0.4558460137859299</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4138811726039719</v>
+        <v>-0.4186363601588425</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2386742733953895</v>
+        <v>-0.2453239935351732</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.264503815868288</v>
+        <v>-0.272561387818115</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.201914879485237</v>
+        <v>-0.2115272773781314</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3972</v>
+        <v>3983</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04104130949074403</v>
+        <v>0.04244072766557139</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1764394729957672</v>
+        <v>-0.1758921641104294</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3317140807860639</v>
+        <v>-0.3307925468302528</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2883409815403439</v>
+        <v>-0.287521018925986</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3609012436580983</v>
+        <v>-0.3624240622230346</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3764583605872716</v>
+        <v>-0.3766633572512958</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3721460745838669</v>
+        <v>-0.3736109394286231</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2976586278293993</v>
+        <v>-0.2993933985763064</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3448485579847045</v>
+        <v>-0.3476998337085107</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3761392163644146</v>
+        <v>-0.3802594483573785</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3655739332088075</v>
+        <v>-0.3697534741497464</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2164752546659727</v>
+        <v>-0.2223031022824173</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1946391732712627</v>
+        <v>-0.201827352358606</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1057474106252698</v>
+        <v>-0.1143942902922177</v>
       </c>
     </row>
     <row r="30">
@@ -5156,153 +5156,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4003</v>
+        <v>4014</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.009123810103098151</v>
+        <v>0.01037488978895595</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2191257848684174</v>
+        <v>-0.2184751991635494</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3513478481638899</v>
+        <v>-0.3503809356246208</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2574706922006911</v>
+        <v>-0.2567452428287496</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3336218660160881</v>
+        <v>-0.3348334596906</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3218221779287802</v>
+        <v>-0.3219903678884819</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3431221277908847</v>
+        <v>-0.3442849509932344</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2478712025779544</v>
+        <v>-0.2493490602279422</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2452551875217139</v>
+        <v>-0.2477919987330708</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3078106023042011</v>
+        <v>-0.3113196149041286</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2988940787766268</v>
+        <v>-0.3024529484487033</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1756355142056591</v>
+        <v>-0.1805754082905082</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2321362847678685</v>
+        <v>-0.2380181929313565</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1421941440545567</v>
+        <v>-0.1493460239995414</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 1.78</t>
+          <t>X &lt; 1.779</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4018</v>
+        <v>4028</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.03735363906821476</v>
+        <v>-0.02310365859151631</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1963204858810599</v>
+        <v>-0.1823978209339217</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3046943075589752</v>
+        <v>-0.3152021892711403</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2106702118353638</v>
+        <v>-0.2214321092478642</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2885311634528094</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3253333864867685</v>
+        <v>-0.3119612860151975</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3220258002866601</v>
+        <v>-0.3096033367788849</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2288657541014345</v>
+        <v>-0.2413942877344297</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.3010533600059659</v>
+        <v>-0.3143553171436935</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3416958580544218</v>
+        <v>-0.3557377886777005</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3335846442713262</v>
+        <v>-0.3476219328820775</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1857907306328954</v>
+        <v>-0.2011630329778598</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2934148917046002</v>
+        <v>-0.309424531843483</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1532050496384301</v>
+        <v>-0.170560254827187</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 1.832</t>
+          <t>X &lt; 1.831</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4045</v>
+        <v>4056</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.06593328041113722</v>
+        <v>-0.06479356487223242</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1606256631594363</v>
+        <v>-0.1601522335433359</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3695165063808332</v>
+        <v>-0.3685120225276961</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1519627913986383</v>
+        <v>-0.1515353805073545</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2328757570317492</v>
+        <v>-0.2338458726335233</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2674380555089613</v>
+        <v>-0.2675041170711268</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2893818486762356</v>
+        <v>-0.2901818399755882</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1505771544232815</v>
+        <v>-0.1517939994902662</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.1979793687888076</v>
+        <v>-0.1998603536826238</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2439929179763993</v>
+        <v>-0.2466108045507198</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1878699035769671</v>
+        <v>-0.1906590407750883</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.04079664988761778</v>
+        <v>-0.04477067257588629</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1504705456626851</v>
+        <v>-0.1549736818223764</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.03437636709061564</v>
+        <v>-0.03996554207680703</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4054</v>
+        <v>4065</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.05898340206127273</v>
+        <v>-0.05792938251327939</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1816249962002416</v>
+        <v>-0.1810985740114432</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3663323029411671</v>
+        <v>-0.3653389690150561</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1981837978357248</v>
+        <v>-0.1976336546888717</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2308965691034786</v>
+        <v>-0.2317626411973848</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2647229231836121</v>
+        <v>-0.2647432335110622</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2621806744800566</v>
+        <v>-0.2629462620180192</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.124712349406451</v>
+        <v>-0.1258875175360927</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1721383022973342</v>
+        <v>-0.1739229748764899</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1952857366889234</v>
+        <v>-0.1978097653343482</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1643780810207218</v>
+        <v>-0.1670035347107728</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.04220393090372454</v>
+        <v>-0.04589162069683539</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1032454468758033</v>
+        <v>-0.1075372554238925</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.03623020309808567</v>
+        <v>-0.04142117793492872</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4069</v>
+        <v>4080</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.03113651069114098</v>
+        <v>-0.03026818941178533</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1347387322725311</v>
+        <v>-0.1343446285179155</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2711872338434205</v>
+        <v>-0.270453933312325</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1276706741544089</v>
+        <v>-0.127314006287115</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1377039796555479</v>
+        <v>-0.1386394913694176</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1702889311491873</v>
+        <v>-0.1704753638159744</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1680446105927089</v>
+        <v>-0.1688845406079977</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.03277847410046064</v>
+        <v>-0.03401603373047379</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.05568587254341395</v>
+        <v>-0.05750857449636726</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1064014675044476</v>
+        <v>-0.1087907401880486</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.07633989433618638</v>
+        <v>-0.07882584709748386</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.003595589903234497</v>
+        <v>-0.006919224598036067</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.01681106944264599</v>
+        <v>-0.02077356110932271</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.001658399076809758</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.002283551901868464</v>
+        <v>-0.001587713829998449</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03738790767243216</v>
+        <v>-0.03725967739971736</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1990650548961028</v>
+        <v>-0.1985278730164097</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.0800110236113909</v>
+        <v>-0.07978482643363094</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.06726742164935473</v>
+        <v>-0.06823500150774464</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.09878638211299062</v>
+        <v>-0.09908806913198731</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.09680102665524259</v>
+        <v>-0.09767720264765245</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.01235658990851363</v>
+        <v>-0.01348883949700053</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.01091227559660268</v>
+        <v>-0.01261698633770436</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.06415965421422243</v>
+        <v>-0.06633952591478476</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.08379445159561527</v>
+        <v>-0.08593540387252574</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.01331170040486285</v>
+        <v>0.0103458882084837</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.02329650189195576</v>
+        <v>0.01971097486332241</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.06693367446176524</v>
+        <v>0.06267759088075309</v>
       </c>
     </row>
   </sheetData>
